--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -204,7 +204,7 @@
     <t>School Choice Funding</t>
   </si>
   <si>
-    <t>Grants &amp; Contributions</t>
+    <t>Philanthropy</t>
   </si>
   <si>
     <t>TUITION &amp; STUDENT FEES</t>
@@ -228,13 +228,13 @@
     <t>Total School Choice Funding</t>
   </si>
   <si>
-    <t>GRANTS &amp; CONTRIBUTIONS</t>
+    <t>PHILANTHROPY</t>
   </si>
   <si>
     <t>Annual Fundraising</t>
   </si>
   <si>
-    <t>Total Grants &amp; Contributions</t>
+    <t>Total Philanthropy</t>
   </si>
   <si>
     <t>TOTAL NET REVENUE</t>
@@ -720,7 +720,7 @@
     <t>Microschool  |  AZ  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 16, 2026</t>
+    <t>Prepared March 17, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -747,7 +747,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>
@@ -817,7 +817,7 @@
     <numFmt numFmtId="169" formatCode="0.00x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -834,7 +834,7 @@
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -883,19 +883,13 @@
     </font>
     <font>
       <color rgb="FF6B7280"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF9CA3AF"/>
-      <sz val="8"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -912,7 +906,7 @@
     </font>
     <font>
       <color rgb="FF94A3B8"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1037,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1089,14 +1083,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3006,14 +2999,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="40" t="s">
         <v>224</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3049,43 +3042,43 @@
     <row r="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="C3" s="42"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="43"/>
+      <c r="C4" s="42"/>
     </row>
     <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="44" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="46"/>
+      <c r="C9" s="45"/>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="46" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="47"/>
+      <c r="C10" s="46"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="44" t="s">
         <v>229</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="47" t="s">
         <v>230</v>
       </c>
     </row>
@@ -3124,7 +3117,7 @@
       <c r="B19" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="48" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3136,88 +3129,88 @@
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="49" t="s">
         <v>236</v>
       </c>
-      <c r="C23" s="51"/>
+      <c r="C23" s="50"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="50" t="s">
+      <c r="B24" s="49" t="s">
         <v>237</v>
       </c>
-      <c r="C24" s="51"/>
+      <c r="C24" s="50"/>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="C25" s="51"/>
+      <c r="C25" s="50"/>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="49" t="s">
         <v>239</v>
       </c>
-      <c r="C26" s="51"/>
+      <c r="C26" s="50"/>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="50" t="s">
+      <c r="B27" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="C27" s="51"/>
+      <c r="C27" s="50"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="49" t="s">
         <v>240</v>
       </c>
-      <c r="C28" s="51"/>
+      <c r="C28" s="50"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="49" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="51"/>
+      <c r="C29" s="50"/>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="49" t="s">
         <v>242</v>
       </c>
-      <c r="C30" s="51"/>
+      <c r="C30" s="50"/>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="50" t="s">
+      <c r="B31" s="49" t="s">
         <v>243</v>
       </c>
-      <c r="C31" s="51"/>
+      <c r="C31" s="50"/>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="50" t="s">
+      <c r="B32" s="49" t="s">
         <v>244</v>
       </c>
-      <c r="C32" s="51"/>
+      <c r="C32" s="50"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="s">
+      <c r="B33" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="C33" s="51"/>
+      <c r="C33" s="50"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="50" t="s">
+      <c r="B34" s="49" t="s">
         <v>246</v>
       </c>
-      <c r="C34" s="51"/>
+      <c r="C34" s="50"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="50" t="s">
+      <c r="B35" s="49" t="s">
         <v>247</v>
       </c>
-      <c r="C35" s="51"/>
+      <c r="C35" s="50"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="50" t="s">
+      <c r="B36" s="49" t="s">
         <v>248</v>
       </c>
-      <c r="C36" s="51"/>
+      <c r="C36" s="50"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="40" t="s">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -57,7 +57,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="249">
   <si>
-    <t>SchoolStack — Assumptions &amp; Drivers</t>
+    <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
   <si>
     <t>Edit the highlighted cells below to update the entire model</t>
@@ -177,7 +177,7 @@
     <t>Enrollment Growth %</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>Capacity Utilization %</t>
@@ -240,7 +240,7 @@
     <t>TOTAL NET REVENUE</t>
   </si>
   <si>
-    <t>SchoolStack — Staffing Plan</t>
+    <t>SchoolStack - Staffing Plan</t>
   </si>
   <si>
     <t>Role</t>
@@ -378,7 +378,7 @@
     <t>% of Revenue</t>
   </si>
   <si>
-    <t>SchoolStack — Capital Stack (2026-27)</t>
+    <t>SchoolStack - Capital Stack (2026-27)</t>
   </si>
   <si>
     <t>SOURCES OF CAPITAL</t>
@@ -414,10 +414,10 @@
     <t>CAPITAL SURPLUS / (GAP)</t>
   </si>
   <si>
-    <t>⚠ Funding gap — additional capital needed</t>
-  </si>
-  <si>
-    <t>SchoolStack — Debt Schedule</t>
+    <t>⚠ Funding gap - additional capital needed</t>
+  </si>
+  <si>
+    <t>SchoolStack - Debt Schedule</t>
   </si>
   <si>
     <t>Loan / Facility</t>
@@ -627,7 +627,7 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>SchoolStack — Underwriting Snapshot</t>
+    <t>SchoolStack - Underwriting Snapshot</t>
   </si>
   <si>
     <t>Bright Horizons Microschool | Microschool | AZ</t>
@@ -3307,19 +3307,19 @@
         <v>40</v>
       </c>
       <c r="C3" s="12">
-        <f>IF(B2=0,"—",(C2-B2)/B2)</f>
+        <f>IF(B2=0,"-",(C2-B2)/B2)</f>
         <v>0.5</v>
       </c>
       <c r="D3" s="12">
-        <f>IF(C2=0,"—",(D2-C2)/C2)</f>
+        <f>IF(C2=0,"-",(D2-C2)/C2)</f>
         <v>0.22</v>
       </c>
       <c r="E3" s="12">
-        <f>IF(D2=0,"—",(E2-D2)/D2)</f>
+        <f>IF(D2=0,"-",(E2-D2)/D2)</f>
         <v>0.14</v>
       </c>
       <c r="F3" s="12" t="str">
-        <f>IF(E2=0,"—",(F2-E2)/E2)</f>
+        <f>IF(E2=0,"-",(F2-E2)/E2)</f>
         <v>0</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -720,7 +720,7 @@
     <t>Microschool  |  AZ  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 17, 2026</t>
+    <t>Prepared March 18, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -747,7 +747,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -23,9 +23,9 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$F23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Enrollment &amp; Rev Drivers'!$A1:$F14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Enrollment &amp; Rev Drivers'!$A1:$F15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Enrollment &amp; Rev Drivers'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Tuition &amp; Funding Detail'!$A1:$F14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Tuition &amp; Funding Detail'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tuition &amp; Funding Detail'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing Plan'!$A1:$H22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing Plan'!$1:$1</definedName>
@@ -33,9 +33,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Facilities &amp; Occupancy'!$A1:$F9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Facilities &amp; Occupancy'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Capital Stack &amp; Startup Uses'!$A1:$B16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Capital Stack &amp; Startup Uses'!$A1:$B17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Capital Stack &amp; Startup Uses'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Debt Schedule'!$A1:$G10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Debt Schedule'!$A1:$G16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Debt Schedule'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Cash Flow Monthly Y1'!$A1:$N13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Cash Flow Monthly Y1'!$1:$1</definedName>
@@ -45,9 +45,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'5-Year Balance Sheet'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'DSCR &amp; Covenants'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'DSCR &amp; Covenants'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'Underwriting Snapshot'!$A1:$C27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'Underwriting Snapshot'!$A1:$C28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="257">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -201,6 +201,9 @@
     <t>Tuition &amp; Student Fees</t>
   </si>
   <si>
+    <t>Tuition Offsets</t>
+  </si>
+  <si>
     <t>School Choice Funding</t>
   </si>
   <si>
@@ -219,6 +222,15 @@
     <t>Total Tuition &amp; Student Fees</t>
   </si>
   <si>
+    <t>TUITION OFFSETS</t>
+  </si>
+  <si>
+    <t>Scholarship Discount</t>
+  </si>
+  <si>
+    <t>Total Tuition Offsets</t>
+  </si>
+  <si>
     <t>SCHOOL CHOICE FUNDING</t>
   </si>
   <si>
@@ -387,6 +399,9 @@
     <t>Founder Equity / Starting Cash</t>
   </si>
   <si>
+    <t>Loan: Equipment Loan</t>
+  </si>
+  <si>
     <t>TOTAL CAPITAL SOURCES</t>
   </si>
   <si>
@@ -441,7 +456,7 @@
     <t>Total Interest</t>
   </si>
   <si>
-    <t>No loans entered</t>
+    <t>Equipment Loan</t>
   </si>
   <si>
     <t>TOTAL DEBT SERVICE</t>
@@ -456,6 +471,12 @@
     <t>AMORTIZATION SCHEDULE (ANNUAL)</t>
   </si>
   <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Equipment Loan Balance</t>
+  </si>
+  <si>
     <t>August</t>
   </si>
   <si>
@@ -588,9 +609,6 @@
     <t>DSCR</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>LIQUIDITY METRICS</t>
   </si>
   <si>
@@ -636,10 +654,16 @@
     <t>POLICY FLAGS</t>
   </si>
   <si>
+    <t>DSCR ≥ 1.20x (2026-27)</t>
+  </si>
+  <si>
+    <t>3.63x</t>
+  </si>
+  <si>
     <t>Min 2 Months Cash Reserve (2026-27)</t>
   </si>
   <si>
-    <t>2.8 months</t>
+    <t>3.6 months</t>
   </si>
   <si>
     <t>Positive Net Income (2026-27)</t>
@@ -666,7 +690,7 @@
     <t>Flags Passed</t>
   </si>
   <si>
-    <t>4 / 5</t>
+    <t>5 / 6</t>
   </si>
   <si>
     <t>Overall Assessment</t>
@@ -702,7 +726,7 @@
     <t>2026-27 Cash Reserve (Months)</t>
   </si>
   <si>
-    <t>2.8</t>
+    <t>3.6</t>
   </si>
   <si>
     <t>Break-Even Year</t>
@@ -1059,15 +1083,13 @@
     <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1690,32 +1712,32 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B2" s="25">
-        <f>'Tuition &amp; Funding Detail'!B14</f>
-        <v>196667</v>
-      </c>
-      <c r="C2" s="25">
-        <f>'Tuition &amp; Funding Detail'!C14</f>
-        <v>362760</v>
-      </c>
-      <c r="D2" s="25">
-        <f>'Tuition &amp; Funding Detail'!D14</f>
-        <v>455954</v>
-      </c>
-      <c r="E2" s="25">
-        <f>'Tuition &amp; Funding Detail'!E14</f>
-        <v>533300</v>
-      </c>
-      <c r="F2" s="25">
-        <f>'Tuition &amp; Funding Detail'!F14</f>
-        <v>549850</v>
+        <v>163</v>
+      </c>
+      <c r="B2" s="26">
+        <f>'Tuition &amp; Funding Detail'!B17</f>
+        <v>184667</v>
+      </c>
+      <c r="C2" s="26">
+        <f>'Tuition &amp; Funding Detail'!C17</f>
+        <v>340512</v>
+      </c>
+      <c r="D2" s="26">
+        <f>'Tuition &amp; Funding Detail'!D17</f>
+        <v>427946</v>
+      </c>
+      <c r="E2" s="26">
+        <f>'Tuition &amp; Funding Detail'!E17</f>
+        <v>500518</v>
+      </c>
+      <c r="F2" s="26">
+        <f>'Tuition &amp; Funding Detail'!F17</f>
+        <v>516085</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B3" s="13">
         <f>'Staffing Plan'!B22</f>
@@ -1740,7 +1762,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B4" s="13">
         <f>'Operating Expenses'!B12+'Facilities &amp; Occupancy'!B6</f>
@@ -1765,122 +1787,122 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B5" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
       <c r="C5" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
       <c r="D5" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
       <c r="E5" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
       <c r="F5" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B6" s="26">
+        <v>156</v>
+      </c>
+      <c r="B6" s="27">
         <f>SUM(B3:B5)</f>
-        <v>159434</v>
-      </c>
-      <c r="C6" s="26">
+        <v>166394</v>
+      </c>
+      <c r="C6" s="27">
         <f>SUM(C3:C5)</f>
-        <v>201888</v>
-      </c>
-      <c r="D6" s="26">
+        <v>208848</v>
+      </c>
+      <c r="D6" s="27">
         <f>SUM(D3:D5)</f>
-        <v>211187</v>
-      </c>
-      <c r="E6" s="26">
+        <v>218147</v>
+      </c>
+      <c r="E6" s="27">
         <f>SUM(E3:E5)</f>
-        <v>219967</v>
-      </c>
-      <c r="F6" s="26">
+        <v>226927</v>
+      </c>
+      <c r="F6" s="27">
         <f>SUM(F3:F5)</f>
-        <v>226410</v>
+        <v>233370</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="27">
+        <v>165</v>
+      </c>
+      <c r="B7" s="28">
         <f>B2-B6</f>
-        <v>37233</v>
-      </c>
-      <c r="C7" s="27">
+        <v>18273</v>
+      </c>
+      <c r="C7" s="28">
         <f>C2-C6</f>
-        <v>160872</v>
-      </c>
-      <c r="D7" s="27">
+        <v>131665</v>
+      </c>
+      <c r="D7" s="28">
         <f>D2-D6</f>
-        <v>244768</v>
-      </c>
-      <c r="E7" s="27">
+        <v>209800</v>
+      </c>
+      <c r="E7" s="28">
         <f>E2-E6</f>
-        <v>313333</v>
-      </c>
-      <c r="F7" s="27">
+        <v>273591</v>
+      </c>
+      <c r="F7" s="28">
         <f>F2-F6</f>
-        <v>323440</v>
+        <v>282716</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B8" s="12">
         <f>IF(B2=0,0,B7/B2)</f>
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="C8" s="12">
         <f>IF(C2=0,0,C7/C2)</f>
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="D8" s="12">
         <f>IF(D2=0,0,D7/D2)</f>
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="E8" s="12">
         <f>IF(E2=0,0,E7/E2)</f>
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="F8" s="12">
         <f>IF(F2=0,0,F7/F2)</f>
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="25">
+        <v>167</v>
+      </c>
+      <c r="B9" s="26">
         <f>B7</f>
-        <v>37233</v>
-      </c>
-      <c r="C9" s="25">
+        <v>18273</v>
+      </c>
+      <c r="C9" s="26">
         <f>B9+C7</f>
-        <v>198105</v>
-      </c>
-      <c r="D9" s="25">
+        <v>149938</v>
+      </c>
+      <c r="D9" s="26">
         <f>C9+D7</f>
-        <v>442873</v>
-      </c>
-      <c r="E9" s="25">
+        <v>359738</v>
+      </c>
+      <c r="E9" s="26">
         <f>D9+E7</f>
-        <v>756206</v>
-      </c>
-      <c r="F9" s="25">
+        <v>633329</v>
+      </c>
+      <c r="F9" s="26">
         <f>E9+F7</f>
-        <v>1079646</v>
+        <v>916045</v>
       </c>
     </row>
   </sheetData>
@@ -1927,7 +1949,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1937,27 +1959,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B3" s="13">
-        <v>37233</v>
+        <v>48273</v>
       </c>
       <c r="C3" s="13">
-        <v>198105</v>
+        <v>179938</v>
       </c>
       <c r="D3" s="13">
-        <v>442873</v>
+        <v>389738</v>
       </c>
       <c r="E3" s="13">
-        <v>756206</v>
+        <v>663329</v>
       </c>
       <c r="F3" s="13">
-        <v>1079646</v>
+        <v>946045</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B4" s="13">
         <v>0</v>
@@ -1977,32 +1999,32 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B5" s="14">
         <f>SUM(B3:B4)</f>
-        <v>37233</v>
+        <v>48273</v>
       </c>
       <c r="C5" s="14">
         <f>SUM(C3:C4)</f>
-        <v>198105</v>
+        <v>179938</v>
       </c>
       <c r="D5" s="14">
         <f>SUM(D3:D4)</f>
-        <v>442873</v>
+        <v>389738</v>
       </c>
       <c r="E5" s="14">
         <f>SUM(E3:E4)</f>
-        <v>756206</v>
+        <v>663329</v>
       </c>
       <c r="F5" s="14">
         <f>SUM(F3:F4)</f>
-        <v>1079646</v>
+        <v>946045</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -2012,27 +2034,27 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B8" s="13">
-        <v>0</v>
+        <v>24840</v>
       </c>
       <c r="C8" s="13">
-        <v>0</v>
+        <v>19371</v>
       </c>
       <c r="D8" s="13">
-        <v>0</v>
+        <v>13573</v>
       </c>
       <c r="E8" s="13">
-        <v>0</v>
+        <v>7428</v>
       </c>
       <c r="F8" s="13">
-        <v>0</v>
+        <v>914</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B9" s="13">
         <v>0</v>
@@ -2052,32 +2074,32 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" s="14" t="str">
+        <v>175</v>
+      </c>
+      <c r="B10" s="14">
         <f>SUM(B8:B9)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="14" t="str">
+        <v>24840</v>
+      </c>
+      <c r="C10" s="14">
         <f>SUM(C8:C9)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="14" t="str">
+        <v>19371</v>
+      </c>
+      <c r="D10" s="14">
         <f>SUM(D8:D9)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="14" t="str">
+        <v>13573</v>
+      </c>
+      <c r="E10" s="14">
         <f>SUM(E8:E9)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="14" t="str">
+        <v>7428</v>
+      </c>
+      <c r="F10" s="14">
         <f>SUM(F8:F9)</f>
-        <v>0</v>
+        <v>914</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2087,90 +2109,90 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B13" s="13">
         <v>0</v>
       </c>
       <c r="C13" s="13">
-        <v>37233</v>
+        <v>23433</v>
       </c>
       <c r="D13" s="13">
-        <v>198105</v>
+        <v>160567</v>
       </c>
       <c r="E13" s="13">
-        <v>442873</v>
+        <v>376165</v>
       </c>
       <c r="F13" s="13">
-        <v>756206</v>
+        <v>655901</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B14" s="13">
-        <v>37233</v>
+        <v>23433</v>
       </c>
       <c r="C14" s="13">
-        <v>160872</v>
+        <v>137134</v>
       </c>
       <c r="D14" s="13">
-        <v>244768</v>
+        <v>215598</v>
       </c>
       <c r="E14" s="13">
-        <v>313333</v>
+        <v>279736</v>
       </c>
       <c r="F14" s="13">
-        <v>323440</v>
+        <v>289230</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B15" s="14">
         <f>B5-B10</f>
-        <v>37233</v>
+        <v>23433</v>
       </c>
       <c r="C15" s="14">
         <f>C5-C10</f>
-        <v>198105</v>
+        <v>160567</v>
       </c>
       <c r="D15" s="14">
         <f>D5-D10</f>
-        <v>442873</v>
+        <v>376165</v>
       </c>
       <c r="E15" s="14">
         <f>E5-E10</f>
-        <v>756206</v>
+        <v>655901</v>
       </c>
       <c r="F15" s="14">
         <f>F5-F10</f>
-        <v>1079646</v>
+        <v>945131</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B17" s="25" t="str">
+        <v>180</v>
+      </c>
+      <c r="B17" s="26" t="str">
         <f>B5-B10-B15</f>
         <v>0</v>
       </c>
-      <c r="C17" s="25" t="str">
+      <c r="C17" s="26" t="str">
         <f>C5-C10-C15</f>
         <v>0</v>
       </c>
-      <c r="D17" s="25" t="str">
+      <c r="D17" s="26" t="str">
         <f>D5-D10-D15</f>
         <v>0</v>
       </c>
-      <c r="E17" s="25" t="str">
+      <c r="E17" s="26" t="str">
         <f>E5-E10-E15</f>
         <v>0</v>
       </c>
-      <c r="F17" s="25" t="str">
+      <c r="F17" s="26" t="str">
         <f>F5-F10-F15</f>
         <v>0</v>
       </c>
@@ -2219,7 +2241,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2229,67 +2251,72 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B3" s="13">
-        <v>37233</v>
+        <v>25233</v>
       </c>
       <c r="C3" s="13">
-        <v>160872</v>
+        <v>138624</v>
       </c>
       <c r="D3" s="13">
-        <v>244767</v>
+        <v>216759</v>
       </c>
       <c r="E3" s="13">
-        <v>313333</v>
+        <v>280551</v>
       </c>
       <c r="F3" s="13">
-        <v>323440</v>
+        <v>289675</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B4" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
       <c r="C4" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
       <c r="D4" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
       <c r="E4" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
       <c r="F4" s="13">
-        <v>0</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>177</v>
+        <v>183</v>
+      </c>
+      <c r="B5" s="29">
+        <f>IF(B4=0,"N/A",B3/B4)</f>
+        <v>3.63</v>
+      </c>
+      <c r="C5" s="29">
+        <f>IF(C4=0,"N/A",C3/C4)</f>
+        <v>19.92</v>
+      </c>
+      <c r="D5" s="29">
+        <f>IF(D4=0,"N/A",D3/D4)</f>
+        <v>31.14</v>
+      </c>
+      <c r="E5" s="29">
+        <f>IF(E4=0,"N/A",E3/E4)</f>
+        <v>40.31</v>
+      </c>
+      <c r="F5" s="29">
+        <f>IF(F4=0,"N/A",F3/F4)</f>
+        <v>41.62</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -2299,27 +2326,27 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B8" s="13">
-        <v>37233</v>
+        <v>48273</v>
       </c>
       <c r="C8" s="13">
-        <v>198105</v>
+        <v>179938</v>
       </c>
       <c r="D8" s="13">
-        <v>442873</v>
+        <v>389738</v>
       </c>
       <c r="E8" s="13">
-        <v>756206</v>
+        <v>663329</v>
       </c>
       <c r="F8" s="13">
-        <v>1079646</v>
+        <v>946045</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B9" s="13">
         <v>13286</v>
@@ -2339,52 +2366,52 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="29">
+        <v>187</v>
+      </c>
+      <c r="B10" s="30">
         <f>IF(B9=0,0,B8/B9)</f>
-        <v>2.8</v>
-      </c>
-      <c r="C10" s="29">
+        <v>3.63</v>
+      </c>
+      <c r="C10" s="30">
         <f>IF(C9=0,0,C8/C9)</f>
-        <v>11.78</v>
-      </c>
-      <c r="D10" s="29">
+        <v>10.7</v>
+      </c>
+      <c r="D10" s="30">
         <f>IF(D9=0,0,D8/D9)</f>
-        <v>25.16</v>
-      </c>
-      <c r="E10" s="29">
+        <v>22.15</v>
+      </c>
+      <c r="E10" s="30">
         <f>IF(E9=0,0,E8/E9)</f>
-        <v>41.25</v>
-      </c>
-      <c r="F10" s="29">
+        <v>36.19</v>
+      </c>
+      <c r="F10" s="30">
         <f>IF(F9=0,0,F8/F9)</f>
-        <v>57.22</v>
+        <v>50.14</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="30">
-        <v>85</v>
-      </c>
-      <c r="C11" s="30">
-        <v>358</v>
-      </c>
-      <c r="D11" s="30">
-        <v>765</v>
-      </c>
-      <c r="E11" s="30">
-        <v>1255</v>
-      </c>
-      <c r="F11" s="30">
-        <v>1741</v>
+        <v>188</v>
+      </c>
+      <c r="B11" s="31">
+        <v>111</v>
+      </c>
+      <c r="C11" s="31">
+        <v>325</v>
+      </c>
+      <c r="D11" s="31">
+        <v>674</v>
+      </c>
+      <c r="E11" s="31">
+        <v>1101</v>
+      </c>
+      <c r="F11" s="31">
+        <v>1525</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2394,27 +2421,32 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>177</v>
+        <v>190</v>
+      </c>
+      <c r="B14" s="32" t="str">
+        <f>IF(B5&gt;=1.2,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="C14" s="32" t="str">
+        <f>IF(C5&gt;=1.2,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="D14" s="32" t="str">
+        <f>IF(D5&gt;=1.2,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="E14" s="32" t="str">
+        <f>IF(E5&gt;=1.2,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="F14" s="32" t="str">
+        <f>IF(F5&gt;=1.2,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B15" s="32" t="str">
         <f>IF(B10&gt;=2,"PASS","FAIL")</f>
@@ -2439,42 +2471,42 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F16" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2492,7 +2524,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2502,204 +2534,215 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B2" s="35"/>
       <c r="C2" s="35"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>187</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>189</v>
+        <v>205</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>193</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>187</v>
+        <v>206</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>195</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>203</v>
-      </c>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B16" s="18">
-        <v>196667</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B17" s="18">
-        <v>159434</v>
+        <v>184667</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B18" s="18">
-        <v>37233</v>
+        <v>166394</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B19" s="37">
-        <v>0.18932001810166424</v>
+        <v>217</v>
+      </c>
+      <c r="B19" s="18">
+        <v>18273</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="18">
-        <v>0</v>
+        <v>218</v>
+      </c>
+      <c r="B20" s="37">
+        <v>0.09895108492583948</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="B21" s="18">
-        <v>37233</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B22" s="18">
-        <v>0</v>
+        <v>48273</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>177</v>
+        <v>220</v>
+      </c>
+      <c r="B23" s="18">
+        <v>30000</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B26" s="18">
-        <v>16389</v>
+        <v>224</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B27" s="18">
-        <v>13286</v>
+        <v>15389</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B28" s="18">
+        <v>13866</v>
       </c>
     </row>
   </sheetData>
@@ -2721,7 +2764,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -2740,7 +2783,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -2750,7 +2793,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -2760,7 +2803,7 @@
     </row>
     <row r="4" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
@@ -2792,221 +2835,241 @@
       <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>Assumptions!$B$17</f>
         <v>12</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>Assumptions!$C$17</f>
         <v>18</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>Assumptions!$D$17</f>
         <v>22</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>Assumptions!$E$17</f>
         <v>25</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>Assumptions!$F$17</f>
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B8" s="25">
+        <v>163</v>
+      </c>
+      <c r="B8" s="26">
         <f>'5-Year P&amp;L'!B2</f>
-        <v>196667</v>
-      </c>
-      <c r="C8" s="25">
+        <v>184667</v>
+      </c>
+      <c r="C8" s="26">
         <f>'5-Year P&amp;L'!C2</f>
-        <v>362760</v>
-      </c>
-      <c r="D8" s="25">
+        <v>340512</v>
+      </c>
+      <c r="D8" s="26">
         <f>'5-Year P&amp;L'!D2</f>
-        <v>455954</v>
-      </c>
-      <c r="E8" s="25">
+        <v>427946</v>
+      </c>
+      <c r="E8" s="26">
         <f>'5-Year P&amp;L'!E2</f>
-        <v>533300</v>
-      </c>
-      <c r="F8" s="25">
+        <v>500518</v>
+      </c>
+      <c r="F8" s="26">
         <f>'5-Year P&amp;L'!F2</f>
-        <v>549850</v>
+        <v>516085</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B9" s="13">
         <f>'5-Year P&amp;L'!B6</f>
-        <v>159434</v>
+        <v>166394</v>
       </c>
       <c r="C9" s="13">
         <f>'5-Year P&amp;L'!C6</f>
-        <v>201888</v>
+        <v>208848</v>
       </c>
       <c r="D9" s="13">
         <f>'5-Year P&amp;L'!D6</f>
-        <v>211187</v>
+        <v>218147</v>
       </c>
       <c r="E9" s="13">
         <f>'5-Year P&amp;L'!E6</f>
-        <v>219967</v>
+        <v>226927</v>
       </c>
       <c r="F9" s="13">
         <f>'5-Year P&amp;L'!F6</f>
-        <v>226410</v>
+        <v>233370</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B10" s="22">
         <f>'5-Year P&amp;L'!B7</f>
-        <v>37233</v>
+        <v>18273</v>
       </c>
       <c r="C10" s="22">
         <f>'5-Year P&amp;L'!C7</f>
-        <v>160872</v>
+        <v>131665</v>
       </c>
       <c r="D10" s="22">
         <f>'5-Year P&amp;L'!D7</f>
-        <v>244768</v>
+        <v>209800</v>
       </c>
       <c r="E10" s="22">
         <f>'5-Year P&amp;L'!E7</f>
-        <v>313333</v>
+        <v>273591</v>
       </c>
       <c r="F10" s="22">
         <f>'5-Year P&amp;L'!F7</f>
-        <v>323440</v>
+        <v>282716</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B11" s="12">
         <f>IF(B8=0,0,B10/B8)</f>
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="C11" s="12">
         <f>IF(C8=0,0,C10/C8)</f>
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="D11" s="12">
         <f>IF(D8=0,0,D10/D8)</f>
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="E11" s="12">
         <f>IF(E8=0,0,E10/E8)</f>
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="F11" s="12">
         <f>IF(F8=0,0,F10/F8)</f>
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="25">
+        <v>167</v>
+      </c>
+      <c r="B12" s="26">
         <f>B10</f>
-        <v>37233</v>
-      </c>
-      <c r="C12" s="25">
+        <v>18273</v>
+      </c>
+      <c r="C12" s="26">
         <f>B12+C10</f>
-        <v>198105</v>
-      </c>
-      <c r="D12" s="25">
+        <v>149938</v>
+      </c>
+      <c r="D12" s="26">
         <f>C12+D10</f>
-        <v>442873</v>
-      </c>
-      <c r="E12" s="25">
+        <v>359738</v>
+      </c>
+      <c r="E12" s="26">
         <f>D12+E10</f>
-        <v>756206</v>
-      </c>
-      <c r="F12" s="25">
+        <v>633329</v>
+      </c>
+      <c r="F12" s="26">
         <f>E12+F10</f>
-        <v>1079646</v>
+        <v>916045</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="25">
-        <v>37233</v>
-      </c>
-      <c r="C13" s="25">
-        <v>198105</v>
-      </c>
-      <c r="D13" s="25">
-        <v>442873</v>
-      </c>
-      <c r="E13" s="25">
-        <v>756206</v>
-      </c>
-      <c r="F13" s="25">
-        <v>1079646</v>
+        <v>230</v>
+      </c>
+      <c r="B13" s="26">
+        <v>48273</v>
+      </c>
+      <c r="C13" s="26">
+        <v>179938</v>
+      </c>
+      <c r="D13" s="26">
+        <v>389738</v>
+      </c>
+      <c r="E13" s="26">
+        <v>663329</v>
+      </c>
+      <c r="F13" s="26">
+        <v>946045</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B14" s="13">
-        <v>16389</v>
+        <v>15389</v>
       </c>
       <c r="C14" s="13">
-        <v>20153</v>
+        <v>18917</v>
       </c>
       <c r="D14" s="13">
-        <v>20725</v>
+        <v>19452</v>
       </c>
       <c r="E14" s="13">
-        <v>21332</v>
+        <v>20021</v>
       </c>
       <c r="F14" s="13">
-        <v>21994</v>
+        <v>20643</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B15" s="13">
-        <v>13286</v>
+        <v>13866</v>
       </c>
       <c r="C15" s="13">
-        <v>11216</v>
+        <v>11603</v>
       </c>
       <c r="D15" s="13">
-        <v>9599</v>
+        <v>9916</v>
       </c>
       <c r="E15" s="13">
-        <v>8799</v>
+        <v>9077</v>
       </c>
       <c r="F15" s="13">
-        <v>9056</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+        <v>9335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="29">
+        <v>3.63</v>
+      </c>
+      <c r="C16" s="29">
+        <v>19.92</v>
+      </c>
+      <c r="D16" s="29">
+        <v>31.14</v>
+      </c>
+      <c r="E16" s="29">
+        <v>40.31</v>
+      </c>
+      <c r="F16" s="29">
+        <v>41.62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3014,7 +3077,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3043,13 +3106,13 @@
     <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="41" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C3" s="41"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="42" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C4" s="42"/>
     </row>
@@ -3059,7 +3122,7 @@
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="44" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
@@ -3070,151 +3133,151 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="46" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C10" s="46"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="44" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="C16" s="25">
-        <v>549850</v>
+        <v>240</v>
+      </c>
+      <c r="C16" s="26">
+        <v>516085</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="C17" s="25">
-        <v>323440</v>
+        <v>241</v>
+      </c>
+      <c r="C17" s="26">
+        <v>282716</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="25">
-        <v>1079646</v>
+        <v>185</v>
+      </c>
+      <c r="C18" s="26">
+        <v>916045</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C19" s="48" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="49" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C23" s="50"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="49" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C24" s="50"/>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="49" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C25" s="50"/>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="49" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C26" s="50"/>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="49" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C27" s="50"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="49" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C28" s="50"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="49" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C29" s="50"/>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="49" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C30" s="50"/>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="49" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C31" s="50"/>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="49" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C32" s="50"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="49" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C33" s="50"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="49" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C34" s="50"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="49" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C35" s="50"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="49" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C36" s="50"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="40" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C39" s="40"/>
     </row>
@@ -3252,7 +3315,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3448,19 +3511,19 @@
         <v>48</v>
       </c>
       <c r="B13" s="13">
-        <v>84000</v>
+        <v>-14400</v>
       </c>
       <c r="C13" s="13">
-        <v>129780</v>
+        <v>-22248</v>
       </c>
       <c r="D13" s="13">
-        <v>163372</v>
+        <v>-28008</v>
       </c>
       <c r="E13" s="13">
-        <v>191225</v>
+        <v>-32782</v>
       </c>
       <c r="F13" s="13">
-        <v>196950</v>
+        <v>-33765</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3468,18 +3531,38 @@
         <v>49</v>
       </c>
       <c r="B14" s="13">
+        <v>84000</v>
+      </c>
+      <c r="C14" s="13">
+        <v>129780</v>
+      </c>
+      <c r="D14" s="13">
+        <v>163372</v>
+      </c>
+      <c r="E14" s="13">
+        <v>191225</v>
+      </c>
+      <c r="F14" s="13">
+        <v>196950</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="13">
         <v>5000</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C15" s="13">
         <v>6000</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D15" s="13">
         <v>7000</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E15" s="13">
         <v>8000</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F15" s="13">
         <v>9000</v>
       </c>
     </row>
@@ -3498,7 +3581,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3552,7 +3635,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3562,7 +3645,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="13">
         <f>ROUND(Assumptions!$B$17*12000,0)</f>
@@ -3587,7 +3670,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="13">
         <f>ROUND(Assumptions!$B$17*250,0)</f>
@@ -3612,7 +3695,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="14">
         <f>SUM(B4:B5)</f>
@@ -3637,7 +3720,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -3647,57 +3730,52 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" s="13">
-        <f>ROUND(Assumptions!$B$17*7000,0)</f>
-        <v>84000</v>
+        <v>-14400</v>
       </c>
       <c r="C8" s="13">
-        <f>ROUND(Assumptions!$C$17*7210,0)</f>
-        <v>129780</v>
+        <v>-22248</v>
       </c>
       <c r="D8" s="13">
-        <f>ROUND(Assumptions!$D$17*7426,0)</f>
-        <v>163372</v>
+        <v>-28008</v>
       </c>
       <c r="E8" s="13">
-        <f>ROUND(Assumptions!$E$17*7649,0)</f>
-        <v>191225</v>
+        <v>-32783</v>
       </c>
       <c r="F8" s="13">
-        <f>ROUND(Assumptions!$F$17*7878,0)</f>
-        <v>196950</v>
+        <v>-33765</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" s="14">
         <f>SUM(B8:B8)</f>
-        <v>84000</v>
+        <v>-14400</v>
       </c>
       <c r="C9" s="14">
         <f>SUM(C8:C8)</f>
-        <v>129780</v>
+        <v>-22248</v>
       </c>
       <c r="D9" s="14">
         <f>SUM(D8:D8)</f>
-        <v>163372</v>
+        <v>-28008</v>
       </c>
       <c r="E9" s="14">
         <f>SUM(E8:E8)</f>
-        <v>191225</v>
+        <v>-32783</v>
       </c>
       <c r="F9" s="14">
         <f>SUM(F8:F8)</f>
-        <v>196950</v>
+        <v>-33765</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -3707,72 +3785,132 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="13">
-        <v>5000</v>
+        <f>ROUND(Assumptions!$B$17*7000,0)</f>
+        <v>84000</v>
       </c>
       <c r="C11" s="13">
-        <v>6000</v>
+        <f>ROUND(Assumptions!$C$17*7210,0)</f>
+        <v>129780</v>
       </c>
       <c r="D11" s="13">
-        <v>7000</v>
+        <f>ROUND(Assumptions!$D$17*7426,0)</f>
+        <v>163372</v>
       </c>
       <c r="E11" s="13">
-        <v>8000</v>
+        <f>ROUND(Assumptions!$E$17*7649,0)</f>
+        <v>191225</v>
       </c>
       <c r="F11" s="13">
-        <v>9000</v>
+        <f>ROUND(Assumptions!$F$17*7878,0)</f>
+        <v>196950</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="14">
         <f>SUM(B11:B11)</f>
-        <v>5000</v>
+        <v>84000</v>
       </c>
       <c r="C12" s="14">
         <f>SUM(C11:C11)</f>
-        <v>6000</v>
+        <v>129780</v>
       </c>
       <c r="D12" s="14">
         <f>SUM(D11:D11)</f>
-        <v>7000</v>
+        <v>163372</v>
       </c>
       <c r="E12" s="14">
         <f>SUM(E11:E11)</f>
-        <v>8000</v>
+        <v>191225</v>
       </c>
       <c r="F12" s="14">
         <f>SUM(F11:F11)</f>
+        <v>196950</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="13">
+        <v>5000</v>
+      </c>
+      <c r="C14" s="13">
+        <v>6000</v>
+      </c>
+      <c r="D14" s="13">
+        <v>7000</v>
+      </c>
+      <c r="E14" s="13">
+        <v>8000</v>
+      </c>
+      <c r="F14" s="13">
         <v>9000</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="14">
-        <f>B6+B9+B12</f>
-        <v>236000</v>
-      </c>
-      <c r="C14" s="14">
-        <f>C6+C9+C12</f>
-        <v>362760</v>
-      </c>
-      <c r="D14" s="14">
-        <f>D6+D9+D12</f>
-        <v>455954</v>
-      </c>
-      <c r="E14" s="14">
-        <f>E6+E9+E12</f>
-        <v>533300</v>
-      </c>
-      <c r="F14" s="14">
-        <f>F6+F9+F12</f>
-        <v>549850</v>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="14">
+        <f>SUM(B14:B14)</f>
+        <v>5000</v>
+      </c>
+      <c r="C15" s="14">
+        <f>SUM(C14:C14)</f>
+        <v>6000</v>
+      </c>
+      <c r="D15" s="14">
+        <f>SUM(D14:D14)</f>
+        <v>7000</v>
+      </c>
+      <c r="E15" s="14">
+        <f>SUM(E14:E14)</f>
+        <v>8000</v>
+      </c>
+      <c r="F15" s="14">
+        <f>SUM(F14:F14)</f>
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="14">
+        <f>B6+B9+B12+B15</f>
+        <v>221600</v>
+      </c>
+      <c r="C17" s="14">
+        <f>C6+C9+C12+C15</f>
+        <v>340512</v>
+      </c>
+      <c r="D17" s="14">
+        <f>D6+D9+D12+D15</f>
+        <v>427946</v>
+      </c>
+      <c r="E17" s="14">
+        <f>E6+E9+E12+E15</f>
+        <v>500517</v>
+      </c>
+      <c r="F17" s="14">
+        <f>F6+F9+F12+F15</f>
+        <v>516085</v>
       </c>
     </row>
   </sheetData>
@@ -3799,7 +3937,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3811,39 +3949,39 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D4" s="15">
         <v>1</v>
@@ -3863,13 +4001,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -3889,13 +4027,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D6" s="15">
         <v>0.5</v>
@@ -3915,7 +4053,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -3927,7 +4065,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B9" s="5">
         <v>3</v>
@@ -3935,7 +4073,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B10" s="5">
         <v>2.5</v>
@@ -3943,7 +4081,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B11" s="19">
         <v>114000</v>
@@ -3951,7 +4089,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B12" s="19">
         <v>20000</v>
@@ -3959,7 +4097,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B13" s="19">
         <v>8721</v>
@@ -3967,7 +4105,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B14" s="19">
         <v>0</v>
@@ -3975,7 +4113,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B15" s="18">
         <v>142721</v>
@@ -3983,7 +4121,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -4013,7 +4151,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B19" s="13">
         <v>142721</v>
@@ -4033,7 +4171,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B20" s="20">
         <f>(1+Assumptions!$B$20)^0</f>
@@ -4058,7 +4196,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B21" s="21">
         <f>Assumptions!$B$22</f>
@@ -4079,7 +4217,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B22" s="14">
         <f>B19*B20*B21</f>
@@ -4149,7 +4287,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4159,7 +4297,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B3" s="13">
         <f>ROUND(Assumptions!$B$17*500,0)</f>
@@ -4184,7 +4322,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B4" s="14">
         <f>SUM(B3:B3)</f>
@@ -4209,7 +4347,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4219,7 +4357,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B6" s="13">
         <f>ROUND(Assumptions!$B$17*300,0)</f>
@@ -4244,7 +4382,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B7" s="14">
         <f>SUM(B6:B6)</f>
@@ -4269,7 +4407,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4279,7 +4417,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B9" s="13">
         <v>3000</v>
@@ -4299,7 +4437,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B10" s="14">
         <f>SUM(B9:B9)</f>
@@ -4324,7 +4462,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B12" s="14">
         <f>B4+B7+B10</f>
@@ -4391,7 +4529,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4401,7 +4539,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B3" s="13">
         <v>30000</v>
@@ -4421,7 +4559,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B4" s="13">
         <v>3600</v>
@@ -4441,7 +4579,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B5" s="13">
         <v>2400</v>
@@ -4461,7 +4599,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B6" s="14">
         <f>SUM(B3:B5)</f>
@@ -4486,7 +4624,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B8" s="13">
         <v>3000</v>
@@ -4506,22 +4644,22 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B9" s="12">
-        <v>0.18305053720247932</v>
+        <v>0.19494549648827347</v>
       </c>
       <c r="C9" s="12">
-        <v>0.10213364207740655</v>
+        <v>0.10880673808852552</v>
       </c>
       <c r="D9" s="12">
-        <v>0.08362850199800857</v>
+        <v>0.08910177919644068</v>
       </c>
       <c r="E9" s="12">
-        <v>0.07358551237577349</v>
+        <v>0.07840507983728856</v>
       </c>
       <c r="F9" s="12">
-        <v>0.07345301744794035</v>
+        <v>0.07825870088018447</v>
       </c>
     </row>
   </sheetData>
@@ -4539,7 +4677,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -4548,100 +4686,108 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B4" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="22" t="str">
-        <f>SUM(B4:B4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="16">
-        <v>6000</v>
-      </c>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="16">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="22">
+        <f>SUM(B4:B5)</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B9" s="16">
-        <v>1800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B10" s="16">
-        <v>6000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B11" s="16">
-        <v>26572</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B12" s="16">
+        <v>26572</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" s="16">
         <v>2019</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="22">
-        <f>SUM(B8:B12)</f>
+    <row r="14" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="22">
+        <f>SUM(B9:B13)</f>
         <v>42391</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="23">
-        <f>B5-B13</f>
-        <v>-42391</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>119</v>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="23">
+        <f>B6-B14</f>
+        <v>-12391</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -4662,7 +4808,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4673,7 +4819,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4684,35 +4830,53 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
+      </c>
+      <c r="B4" s="13">
+        <v>30000</v>
+      </c>
+      <c r="C4" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="D4" s="25">
+        <v>5</v>
+      </c>
+      <c r="E4" s="13">
+        <v>6960</v>
+      </c>
+      <c r="F4" s="13">
+        <v>580</v>
+      </c>
+      <c r="G4" s="13">
+        <v>4799</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4723,23 +4887,23 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B7" s="18">
-        <v>0</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B8" s="19">
-        <v>0</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -4747,6 +4911,54 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="13">
+        <v>24840</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="13">
+        <v>19371</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="13">
+        <v>13573</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="13">
+        <v>7428</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="13">
+        <v>914</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4782,90 +4994,90 @@
         <v>17</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B2" s="13">
         <v>155900</v>
       </c>
       <c r="C2" s="13">
-        <v>8900</v>
+        <v>7460</v>
       </c>
       <c r="D2" s="13">
-        <v>8900</v>
+        <v>7460</v>
       </c>
       <c r="E2" s="13">
-        <v>8900</v>
+        <v>7460</v>
       </c>
       <c r="F2" s="13">
-        <v>8900</v>
+        <v>7460</v>
       </c>
       <c r="G2" s="13">
-        <v>8900</v>
+        <v>7460</v>
       </c>
       <c r="H2" s="13">
-        <v>8900</v>
+        <v>7460</v>
       </c>
       <c r="I2" s="13">
-        <v>8900</v>
+        <v>7460</v>
       </c>
       <c r="J2" s="13">
-        <v>8900</v>
+        <v>7460</v>
       </c>
       <c r="K2" s="13">
-        <v>-30433</v>
+        <v>-29473</v>
       </c>
       <c r="L2" s="13">
-        <v>0</v>
+        <v>-1440</v>
       </c>
       <c r="M2" s="13">
         <v>0</v>
       </c>
-      <c r="N2" s="25">
+      <c r="N2" s="26">
         <f>SUM(B2:M2)</f>
-        <v>196667</v>
+        <v>184667</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B3" s="13">
         <v>11893</v>
@@ -4910,7 +5122,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B4" s="13">
         <v>4050</v>
@@ -4955,223 +5167,223 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="C5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="D5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="E5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="F5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="G5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="H5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="I5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="J5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="K5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="L5" s="13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="M5" s="13">
-        <v>0</v>
-      </c>
-      <c r="N5" s="13" t="str">
+        <v>580</v>
+      </c>
+      <c r="N5" s="13">
         <f>SUM(B5:M5)</f>
-        <v>0</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B6" s="22">
         <f>SUM(B3:B5)</f>
-        <v>15943</v>
+        <v>16523</v>
       </c>
       <c r="C6" s="22">
         <f>SUM(C3:C5)</f>
-        <v>15943</v>
+        <v>16523</v>
       </c>
       <c r="D6" s="22">
         <f>SUM(D3:D5)</f>
-        <v>15943</v>
+        <v>16523</v>
       </c>
       <c r="E6" s="22">
         <f>SUM(E3:E5)</f>
-        <v>15943</v>
+        <v>16523</v>
       </c>
       <c r="F6" s="22">
         <f>SUM(F3:F5)</f>
-        <v>15943</v>
+        <v>16523</v>
       </c>
       <c r="G6" s="22">
         <f>SUM(G3:G5)</f>
-        <v>15943</v>
+        <v>16523</v>
       </c>
       <c r="H6" s="22">
         <f>SUM(H3:H5)</f>
-        <v>15943</v>
+        <v>16523</v>
       </c>
       <c r="I6" s="22">
         <f>SUM(I3:I5)</f>
-        <v>15943</v>
+        <v>16523</v>
       </c>
       <c r="J6" s="22">
         <f>SUM(J3:J5)</f>
-        <v>15943</v>
+        <v>16523</v>
       </c>
       <c r="K6" s="22">
         <f>SUM(K3:K5)</f>
-        <v>15947</v>
-      </c>
-      <c r="L6" s="22" t="str">
+        <v>16527</v>
+      </c>
+      <c r="L6" s="22">
         <f>SUM(L3:L5)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="22" t="str">
+        <v>580</v>
+      </c>
+      <c r="M6" s="22">
         <f>SUM(M3:M5)</f>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="N6" s="22">
         <f>SUM(B6:M6)</f>
-        <v>159434</v>
+        <v>166394</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="25">
+        <v>157</v>
+      </c>
+      <c r="B7" s="26">
         <f>B2-B6</f>
-        <v>139957</v>
-      </c>
-      <c r="C7" s="25">
+        <v>139377</v>
+      </c>
+      <c r="C7" s="26">
         <f>C2-C6</f>
-        <v>-7043</v>
-      </c>
-      <c r="D7" s="25">
+        <v>-9063</v>
+      </c>
+      <c r="D7" s="26">
         <f>D2-D6</f>
-        <v>-7043</v>
-      </c>
-      <c r="E7" s="25">
+        <v>-9063</v>
+      </c>
+      <c r="E7" s="26">
         <f>E2-E6</f>
-        <v>-7043</v>
-      </c>
-      <c r="F7" s="25">
+        <v>-9063</v>
+      </c>
+      <c r="F7" s="26">
         <f>F2-F6</f>
-        <v>-7043</v>
-      </c>
-      <c r="G7" s="25">
+        <v>-9063</v>
+      </c>
+      <c r="G7" s="26">
         <f>G2-G6</f>
-        <v>-7043</v>
-      </c>
-      <c r="H7" s="25">
+        <v>-9063</v>
+      </c>
+      <c r="H7" s="26">
         <f>H2-H6</f>
-        <v>-7043</v>
-      </c>
-      <c r="I7" s="25">
+        <v>-9063</v>
+      </c>
+      <c r="I7" s="26">
         <f>I2-I6</f>
-        <v>-7043</v>
-      </c>
-      <c r="J7" s="25">
+        <v>-9063</v>
+      </c>
+      <c r="J7" s="26">
         <f>J2-J6</f>
-        <v>-7043</v>
-      </c>
-      <c r="K7" s="25">
+        <v>-9063</v>
+      </c>
+      <c r="K7" s="26">
         <f>K2-K6</f>
-        <v>-46380</v>
-      </c>
-      <c r="L7" s="25" t="str">
+        <v>-46000</v>
+      </c>
+      <c r="L7" s="26">
         <f>L2-L6</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="25" t="str">
+        <v>-2020</v>
+      </c>
+      <c r="M7" s="26">
         <f>M2-M6</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="25">
+        <v>-580</v>
+      </c>
+      <c r="N7" s="26">
         <f>SUM(B7:M7)</f>
-        <v>37233</v>
+        <v>18273</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B8" s="25">
-        <f>0+B7</f>
-        <v>139957</v>
-      </c>
-      <c r="C8" s="25">
+        <v>158</v>
+      </c>
+      <c r="B8" s="26">
+        <f>30000+B7</f>
+        <v>169377</v>
+      </c>
+      <c r="C8" s="26">
         <f>B8+C7</f>
-        <v>132914</v>
-      </c>
-      <c r="D8" s="25">
+        <v>160314</v>
+      </c>
+      <c r="D8" s="26">
         <f>C8+D7</f>
-        <v>125871</v>
-      </c>
-      <c r="E8" s="25">
+        <v>151251</v>
+      </c>
+      <c r="E8" s="26">
         <f>D8+E7</f>
-        <v>118828</v>
-      </c>
-      <c r="F8" s="25">
+        <v>142188</v>
+      </c>
+      <c r="F8" s="26">
         <f>E8+F7</f>
-        <v>111785</v>
-      </c>
-      <c r="G8" s="25">
+        <v>133125</v>
+      </c>
+      <c r="G8" s="26">
         <f>F8+G7</f>
-        <v>104742</v>
-      </c>
-      <c r="H8" s="25">
+        <v>124062</v>
+      </c>
+      <c r="H8" s="26">
         <f>G8+H7</f>
-        <v>97699</v>
-      </c>
-      <c r="I8" s="25">
+        <v>114999</v>
+      </c>
+      <c r="I8" s="26">
         <f>H8+I7</f>
-        <v>90656</v>
-      </c>
-      <c r="J8" s="25">
+        <v>105936</v>
+      </c>
+      <c r="J8" s="26">
         <f>I8+J7</f>
-        <v>83613</v>
-      </c>
-      <c r="K8" s="25">
+        <v>96873</v>
+      </c>
+      <c r="K8" s="26">
         <f>J8+K7</f>
-        <v>37233</v>
-      </c>
-      <c r="L8" s="25">
+        <v>50873</v>
+      </c>
+      <c r="L8" s="26">
         <f>K8+L7</f>
-        <v>37233</v>
-      </c>
-      <c r="M8" s="25">
+        <v>48853</v>
+      </c>
+      <c r="M8" s="26">
         <f>L8+M7</f>
-        <v>37233</v>
-      </c>
-      <c r="N8" s="25">
+        <v>48273</v>
+      </c>
+      <c r="N8" s="26">
         <f>M8</f>
-        <v>37233</v>
+        <v>48273</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -5189,28 +5401,28 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B11" s="19">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B12" s="18">
         <f>M8</f>
-        <v>37233</v>
+        <v>48273</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B13" s="19">
         <f>MIN(B8:M8)</f>
-        <v>37233</v>
+        <v>48273</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -744,7 +744,7 @@
     <t>Microschool  |  AZ  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 18, 2026</t>
+    <t>Prepared March 26, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -771,7 +771,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -841,7 +841,7 @@
     <numFmt numFmtId="169" formatCode="0.00x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -879,6 +879,11 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -970,7 +975,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1013,17 +1018,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFD0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFD97706"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF93C5FD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1065,9 +1064,9 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1082,7 +1081,7 @@
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1096,22 +1095,22 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -55,12 +55,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="258">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
   <si>
-    <t>Edit the highlighted cells below to update the entire model</t>
+    <t/>
+  </si>
+  <si>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -97,9 +103,6 @@
   </si>
   <si>
     <t>Planned Opening Year</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Max Student Capacity</t>
@@ -857,7 +860,7 @@
     </font>
     <font>
       <i/>
-      <color rgb="FF6B7280"/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -956,12 +959,22 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -971,11 +984,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -994,12 +1002,30 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF93C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1014,15 +1040,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF93C5FD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1054,64 +1071,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1471,202 +1489,205 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>4</v>
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
+      <c r="A5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>8</v>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="9">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="C17" s="9">
+        <v>18</v>
+      </c>
+      <c r="D17" s="9">
+        <v>22</v>
+      </c>
+      <c r="E17" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="F17" s="9">
         <v>25</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="7">
-        <v>12</v>
-      </c>
-      <c r="C17" s="7">
-        <v>18</v>
-      </c>
-      <c r="D17" s="7">
-        <v>22</v>
-      </c>
-      <c r="E17" s="7">
-        <v>25</v>
-      </c>
-      <c r="F17" s="7">
-        <v>25</v>
-      </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="A19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="A20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="10">
         <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="8">
+      <c r="A21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="10">
         <v>0.025</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="9">
+      <c r="A22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="11">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>33</v>
       </c>
+      <c r="B23" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -1690,216 +1711,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="27">
         <f>'Tuition &amp; Funding Detail'!B17</f>
         <v>184667</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="27">
         <f>'Tuition &amp; Funding Detail'!C17</f>
         <v>340512</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="27">
         <f>'Tuition &amp; Funding Detail'!D17</f>
         <v>427946</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="27">
         <f>'Tuition &amp; Funding Detail'!E17</f>
         <v>500518</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="27">
         <f>'Tuition &amp; Funding Detail'!F17</f>
         <v>516085</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="15">
         <f>'Staffing Plan'!B22</f>
         <v>118934</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <f>'Staffing Plan'!C22</f>
         <v>147003</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <f>'Staffing Plan'!D22</f>
         <v>151413</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <f>'Staffing Plan'!E22</f>
         <v>155955</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <f>'Staffing Plan'!F22</f>
         <v>160634</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="15">
         <f>'Operating Expenses'!B12+'Facilities &amp; Occupancy'!B6</f>
         <v>40500</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <f>'Operating Expenses'!C12+'Facilities &amp; Occupancy'!C6</f>
         <v>54885</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <f>'Operating Expenses'!D12+'Facilities &amp; Occupancy'!D6</f>
         <v>59774</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <f>'Operating Expenses'!E12+'Facilities &amp; Occupancy'!E6</f>
         <v>64012</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <f>'Operating Expenses'!F12+'Facilities &amp; Occupancy'!F6</f>
         <v>65776</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="15">
         <v>6960</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <v>6960</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="15">
         <v>6960</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="15">
         <v>6960</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="27">
+      <c r="A6" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="28">
         <f>SUM(B3:B5)</f>
         <v>166394</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>SUM(C3:C5)</f>
         <v>208848</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>SUM(D3:D5)</f>
         <v>218147</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>SUM(E3:E5)</f>
         <v>226927</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>SUM(F3:F5)</f>
         <v>233370</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="28">
+      <c r="A7" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="29">
         <f>B2-B6</f>
         <v>18273</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>C2-C6</f>
         <v>131665</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <f>D2-D6</f>
         <v>209800</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="29">
         <f>E2-E6</f>
         <v>273591</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="29">
         <f>F2-F6</f>
         <v>282716</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="14">
         <f>IF(B2=0,0,B7/B2)</f>
         <v>0.1</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="14">
         <f>IF(C2=0,0,C7/C2)</f>
         <v>0.39</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="14">
         <f>IF(D2=0,0,D7/D2)</f>
         <v>0.49</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="14">
         <f>IF(E2=0,0,E7/E2)</f>
         <v>0.55</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="14">
         <f>IF(F2=0,0,F7/F2)</f>
         <v>0.55</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B9" s="26">
+      <c r="A9" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" s="27">
         <f>B7</f>
         <v>18273</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <f>B9+C7</f>
         <v>149938</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>C9+D7</f>
         <v>359738</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>D9+E7</f>
         <v>633329</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>E9+F7</f>
         <v>916045</v>
       </c>
@@ -1927,271 +1948,271 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="15">
         <v>48273</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <v>179938</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <v>389738</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <v>663329</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <v>946045</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="15">
         <v>0</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <v>0</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <v>0</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>0</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="A5" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="16">
         <f>SUM(B3:B4)</f>
         <v>48273</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="16">
         <f>SUM(C3:C4)</f>
         <v>179938</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="16">
         <f>SUM(D3:D4)</f>
         <v>389738</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="16">
         <f>SUM(E3:E4)</f>
         <v>663329</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="16">
         <f>SUM(F3:F4)</f>
         <v>946045</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="15">
         <v>24840</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="15">
         <v>19371</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="15">
         <v>13573</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="15">
         <v>7428</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>914</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="15">
         <v>0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>0</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="14">
+      <c r="A10" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="16">
         <f>SUM(B8:B9)</f>
         <v>24840</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="16">
         <f>SUM(C8:C9)</f>
         <v>19371</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="16">
         <f>SUM(D8:D9)</f>
         <v>13573</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="16">
         <f>SUM(E8:E9)</f>
         <v>7428</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="16">
         <f>SUM(F8:F9)</f>
         <v>914</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" s="15">
         <v>0</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="15">
         <v>23433</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="15">
         <v>160567</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <v>376165</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="15">
         <v>655901</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B14" s="15">
         <v>23433</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <v>137134</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="15">
         <v>215598</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="15">
         <v>279736</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <v>289230</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15" s="14">
+      <c r="A15" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B15" s="16">
         <f>B5-B10</f>
         <v>23433</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="16">
         <f>C5-C10</f>
         <v>160567</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="16">
         <f>D5-D10</f>
         <v>376165</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="16">
         <f>E5-E10</f>
         <v>655901</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="16">
         <f>F5-F10</f>
         <v>945131</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B17" s="26" t="str">
+      <c r="A17" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="27" t="str">
         <f>B5-B10-B15</f>
         <v>0</v>
       </c>
-      <c r="C17" s="26" t="str">
+      <c r="C17" s="27" t="str">
         <f>C5-C10-C15</f>
         <v>0</v>
       </c>
-      <c r="D17" s="26" t="str">
+      <c r="D17" s="27" t="str">
         <f>D5-D10-D15</f>
         <v>0</v>
       </c>
-      <c r="E17" s="26" t="str">
+      <c r="E17" s="27" t="str">
         <f>E5-E10-E15</f>
         <v>0</v>
       </c>
-      <c r="F17" s="26" t="str">
+      <c r="F17" s="27" t="str">
         <f>F5-F10-F15</f>
         <v>0</v>
       </c>
@@ -2219,293 +2240,293 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="15">
         <v>25233</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <v>138624</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <v>216759</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <v>280551</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <v>289675</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="15">
         <v>6960</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <v>6960</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <v>6960</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>6960</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>6960</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="A5" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="30">
         <f>IF(B4=0,"N/A",B3/B4)</f>
         <v>3.63</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>IF(C4=0,"N/A",C3/C4)</f>
         <v>19.92</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>IF(D4=0,"N/A",D3/D4)</f>
         <v>31.14</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>IF(E4=0,"N/A",E3/E4)</f>
         <v>40.31</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>IF(F4=0,"N/A",F3/F4)</f>
         <v>41.62</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="15">
         <v>48273</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="15">
         <v>179938</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="15">
         <v>389738</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="15">
         <v>663329</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>946045</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="15">
         <v>13286</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>16824</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>17599</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>18331</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>18868</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B10" s="30">
+      <c r="A10" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="31">
         <f>IF(B9=0,0,B8/B9)</f>
         <v>3.63</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>IF(C9=0,0,C8/C9)</f>
         <v>10.7</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>IF(D9=0,0,D8/D9)</f>
         <v>22.15</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>IF(E9=0,0,E8/E9)</f>
         <v>36.19</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>IF(F9=0,0,F8/F9)</f>
         <v>50.14</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B11" s="31">
+      <c r="A11" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="32">
         <v>111</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <v>325</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <v>674</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <v>1101</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <v>1525</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B14" s="32" t="str">
+      <c r="A14" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" s="33" t="str">
         <f>IF(B5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C14" s="32" t="str">
+      <c r="C14" s="33" t="str">
         <f>IF(C5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D14" s="32" t="str">
+      <c r="D14" s="33" t="str">
         <f>IF(D5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E14" s="32" t="str">
+      <c r="E14" s="33" t="str">
         <f>IF(E5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F14" s="32" t="str">
+      <c r="F14" s="33" t="str">
         <f>IF(F5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B15" s="32" t="str">
+      <c r="A15" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="33" t="str">
         <f>IF(B10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C15" s="33" t="str">
         <f>IF(C10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D15" s="32" t="str">
+      <c r="D15" s="33" t="str">
         <f>IF(D10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E15" s="32" t="str">
+      <c r="E15" s="33" t="str">
         <f>IF(E10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F15" s="32" t="str">
+      <c r="F15" s="33" t="str">
         <f>IF(F10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B16" s="32" t="s">
+      <c r="A16" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C16" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>193</v>
+      <c r="B16" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="B17" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>193</v>
+      <c r="D17" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2532,213 +2553,213 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="C9" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>204</v>
-      </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>211</v>
       </c>
+      <c r="B13" s="7" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="6" t="s">
         <v>213</v>
       </c>
+      <c r="B14" s="37" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="A16" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>215</v>
+      <c r="A17" s="6" t="s">
+        <v>216</v>
       </c>
       <c r="B17" s="18">
         <v>184667</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>216</v>
+      <c r="A18" s="6" t="s">
+        <v>217</v>
       </c>
       <c r="B18" s="18">
         <v>166394</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>217</v>
+      <c r="A19" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="B19" s="18">
         <v>18273</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B20" s="37">
+      <c r="A20" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B20" s="38">
         <v>0.09895108492583948</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>160</v>
+      <c r="A21" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="B21" s="18">
         <v>30000</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>219</v>
+      <c r="A22" s="6" t="s">
+        <v>220</v>
       </c>
       <c r="B22" s="18">
         <v>48273</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>220</v>
+      <c r="A23" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="B23" s="18">
         <v>30000</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>200</v>
+      <c r="A24" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>223</v>
       </c>
+      <c r="B25" s="7" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>34</v>
+      <c r="A26" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>225</v>
+      <c r="A27" s="6" t="s">
+        <v>226</v>
       </c>
       <c r="B27" s="18">
         <v>15389</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>226</v>
+      <c r="A28" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="B28" s="18">
         <v>13866</v>
@@ -2771,304 +2792,304 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="A1" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="A2" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
+      <c r="A3" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="A4" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="A6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="E6" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F6" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="31">
+      <c r="A7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="32">
         <f>Assumptions!$B$17</f>
         <v>12</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>Assumptions!$C$17</f>
         <v>18</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>Assumptions!$D$17</f>
         <v>22</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>Assumptions!$E$17</f>
         <v>25</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>Assumptions!$F$17</f>
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="26">
+      <c r="A8" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="27">
         <f>'5-Year P&amp;L'!B2</f>
         <v>184667</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>'5-Year P&amp;L'!C2</f>
         <v>340512</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>'5-Year P&amp;L'!D2</f>
         <v>427946</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>'5-Year P&amp;L'!E2</f>
         <v>500518</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>'5-Year P&amp;L'!F2</f>
         <v>516085</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="15">
         <f>'5-Year P&amp;L'!B6</f>
         <v>166394</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <f>'5-Year P&amp;L'!C6</f>
         <v>208848</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <f>'5-Year P&amp;L'!D6</f>
         <v>218147</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <f>'5-Year P&amp;L'!E6</f>
         <v>226927</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <f>'5-Year P&amp;L'!F6</f>
         <v>233370</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="A10" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="23">
         <f>'5-Year P&amp;L'!B7</f>
         <v>18273</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <f>'5-Year P&amp;L'!C7</f>
         <v>131665</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="23">
         <f>'5-Year P&amp;L'!D7</f>
         <v>209800</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="23">
         <f>'5-Year P&amp;L'!E7</f>
         <v>273591</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="23">
         <f>'5-Year P&amp;L'!F7</f>
         <v>282716</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="14">
         <f>IF(B8=0,0,B10/B8)</f>
         <v>0.1</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="14">
         <f>IF(C8=0,0,C10/C8)</f>
         <v>0.39</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <f>IF(D8=0,0,D10/D8)</f>
         <v>0.49</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <f>IF(E8=0,0,E10/E8)</f>
         <v>0.55</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="14">
         <f>IF(F8=0,0,F10/F8)</f>
         <v>0.55</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B12" s="26">
+      <c r="A12" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="27">
         <f>B10</f>
         <v>18273</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>B12+C10</f>
         <v>149938</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>C12+D10</f>
         <v>359738</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>D12+E10</f>
         <v>633329</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>E12+F10</f>
         <v>916045</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B13" s="26">
+      <c r="A13" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="27">
         <v>48273</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <v>179938</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <v>389738</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <v>663329</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <v>946045</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="15">
         <v>15389</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <v>18917</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="15">
         <v>19452</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="15">
         <v>20021</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <v>20643</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="13">
+      <c r="A15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="15">
         <v>13866</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="15">
         <v>11603</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="15">
         <v>9916</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="15">
         <v>9077</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="15">
         <v>9335</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="29">
+      <c r="A16" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" s="30">
         <v>3.63</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>19.92</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>31.14</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>40.31</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>41.62</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="40" t="s">
-        <v>232</v>
-      </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
+      <c r="A18" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3104,181 +3125,181 @@
     <row r="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="42"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="43"/>
+    </row>
+    <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="45" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="46"/>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="47"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" s="27">
+        <v>516085</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" s="27">
+        <v>282716</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="27">
+        <v>916045</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="C23" s="51"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="C24" s="51"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="50" t="s">
+        <v>247</v>
+      </c>
+      <c r="C25" s="51"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="C26" s="51"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="51"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="50" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" s="51"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="C29" s="51"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="50" t="s">
+        <v>251</v>
+      </c>
+      <c r="C30" s="51"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="50" t="s">
+        <v>252</v>
+      </c>
+      <c r="C31" s="51"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="C32" s="51"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="C33" s="51"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="51"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="C35" s="51"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="C36" s="51"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="41" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="41"/>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
-        <v>234</v>
-      </c>
-      <c r="C4" s="42"/>
-    </row>
-    <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="44" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="45"/>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="C10" s="46"/>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="44" t="s">
-        <v>237</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="C16" s="26">
-        <v>516085</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="C17" s="26">
-        <v>282716</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="C18" s="26">
-        <v>916045</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="49" t="s">
-        <v>244</v>
-      </c>
-      <c r="C23" s="50"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="C24" s="50"/>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="49" t="s">
-        <v>246</v>
-      </c>
-      <c r="C25" s="50"/>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="49" t="s">
-        <v>247</v>
-      </c>
-      <c r="C26" s="50"/>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="C27" s="50"/>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="49" t="s">
-        <v>248</v>
-      </c>
-      <c r="C28" s="50"/>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="49" t="s">
-        <v>249</v>
-      </c>
-      <c r="C29" s="50"/>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="C30" s="50"/>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="49" t="s">
-        <v>251</v>
-      </c>
-      <c r="C31" s="50"/>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="49" t="s">
-        <v>252</v>
-      </c>
-      <c r="C32" s="50"/>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="49" t="s">
-        <v>253</v>
-      </c>
-      <c r="C33" s="50"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="49" t="s">
-        <v>254</v>
-      </c>
-      <c r="C34" s="50"/>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="49" t="s">
-        <v>255</v>
-      </c>
-      <c r="C35" s="50"/>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="49" t="s">
-        <v>256</v>
-      </c>
-      <c r="C36" s="50"/>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="40" t="s">
-        <v>232</v>
-      </c>
-      <c r="C39" s="40"/>
+      <c r="C39" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3322,246 +3343,246 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="10">
+      <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="12">
         <v>12</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="12">
         <v>18</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="12">
         <v>22</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="12">
         <v>25</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="12">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="12">
+      <c r="B3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="14">
         <f>IF(B2=0,"-",(C2-B2)/B2)</f>
         <v>0.5</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="14">
         <f>IF(C2=0,"-",(D2-C2)/C2)</f>
         <v>0.22</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="14">
         <f>IF(D2=0,"-",(E2-D2)/D2)</f>
         <v>0.14</v>
       </c>
-      <c r="F3" s="12" t="str">
+      <c r="F3" s="14" t="str">
         <f>IF(E2=0,"-",(F2-E2)/E2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="A4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="14">
         <v>0.48</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="14">
         <v>0.72</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="14">
         <v>0.88</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="14">
         <v>1</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="A6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="A7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="15">
         <v>12000</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="15">
         <v>12360</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="15">
         <v>12731</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="15">
         <v>13113</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="15">
         <v>13506</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="15">
         <v>250</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="15">
         <v>250</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="15">
         <v>250</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="15">
         <v>250</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="15">
         <v>7000</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>7210</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>7426</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>7649</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>7878</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="A11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="13">
+      <c r="A12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="15">
         <v>147000</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="15">
         <v>226980</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="15">
         <v>285582</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="15">
         <v>334075</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="15">
         <v>343900</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="15">
         <v>-14400</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="15">
         <v>-22248</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="15">
         <v>-28008</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <v>-32782</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="15">
         <v>-33765</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="15">
         <v>84000</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <v>129780</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="15">
         <v>163372</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="15">
         <v>191225</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <v>196950</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="13">
+      <c r="A15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="15">
         <v>5000</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="15">
         <v>6000</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="15">
         <v>7000</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="15">
         <v>8000</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="15">
         <v>9000</v>
       </c>
     </row>
@@ -3588,326 +3609,326 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="10">
+      <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="12">
         <f>Assumptions!$B$17</f>
         <v>12</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="12">
         <f>Assumptions!$C$17</f>
         <v>18</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="12">
         <f>Assumptions!$D$17</f>
         <v>22</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="12">
         <f>Assumptions!$E$17</f>
         <v>25</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="12">
         <f>Assumptions!$F$17</f>
         <v>25</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="A3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="15">
         <f>ROUND(Assumptions!$B$17*12000,0)</f>
         <v>144000</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <f>ROUND(Assumptions!$C$17*12360,0)</f>
         <v>222480</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <f>ROUND(Assumptions!$D$17*12731,0)</f>
         <v>280082</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <f>ROUND(Assumptions!$E$17*13113,0)</f>
         <v>327825</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <f>ROUND(Assumptions!$F$17*13506,0)</f>
         <v>337650</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="15">
         <f>ROUND(Assumptions!$B$17*250,0)</f>
         <v>3000</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <f>ROUND(Assumptions!$C$17*250,0)</f>
         <v>4500</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="15">
         <f>ROUND(Assumptions!$D$17*250,0)</f>
         <v>5500</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="15">
         <f>ROUND(Assumptions!$E$17*250,0)</f>
         <v>6250</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <f>ROUND(Assumptions!$F$17*250,0)</f>
         <v>6250</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="14">
+      <c r="A6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="16">
         <f>SUM(B4:B5)</f>
         <v>147000</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="16">
         <f>SUM(C4:C5)</f>
         <v>226980</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="16">
         <f>SUM(D4:D5)</f>
         <v>285582</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="16">
         <f>SUM(E4:E5)</f>
         <v>334075</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="16">
         <f>SUM(F4:F5)</f>
         <v>343900</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="15">
         <v>-14400</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="15">
         <v>-22248</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="15">
         <v>-28008</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="15">
         <v>-32783</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>-33765</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="14">
+      <c r="A9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="16">
         <f>SUM(B8:B8)</f>
         <v>-14400</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="16">
         <f>SUM(C8:C8)</f>
         <v>-22248</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="16">
         <f>SUM(D8:D8)</f>
         <v>-28008</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="16">
         <f>SUM(E8:E8)</f>
         <v>-32783</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="16">
         <f>SUM(F8:F8)</f>
         <v>-33765</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="13">
+      <c r="A11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="15">
         <f>ROUND(Assumptions!$B$17*7000,0)</f>
         <v>84000</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="15">
         <f>ROUND(Assumptions!$C$17*7210,0)</f>
         <v>129780</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="15">
         <f>ROUND(Assumptions!$D$17*7426,0)</f>
         <v>163372</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="15">
         <f>ROUND(Assumptions!$E$17*7649,0)</f>
         <v>191225</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="15">
         <f>ROUND(Assumptions!$F$17*7878,0)</f>
         <v>196950</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="14">
+      <c r="A12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="16">
         <f>SUM(B11:B11)</f>
         <v>84000</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="16">
         <f>SUM(C11:C11)</f>
         <v>129780</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="16">
         <f>SUM(D11:D11)</f>
         <v>163372</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="16">
         <f>SUM(E11:E11)</f>
         <v>191225</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="16">
         <f>SUM(F11:F11)</f>
         <v>196950</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="15">
         <v>5000</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <v>6000</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="15">
         <v>7000</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="15">
         <v>8000</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <v>9000</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="14">
+      <c r="A15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="16">
         <f>SUM(B14:B14)</f>
         <v>5000</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="16">
         <f>SUM(C14:C14)</f>
         <v>6000</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="16">
         <f>SUM(D14:D14)</f>
         <v>7000</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="16">
         <f>SUM(E14:E14)</f>
         <v>8000</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="16">
         <f>SUM(F14:F14)</f>
         <v>9000</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="14">
+      <c r="A17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="16">
         <f>B6+B9+B12+B15</f>
         <v>221600</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="16">
         <f>C6+C9+C12+C15</f>
         <v>340512</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="16">
         <f>D6+D9+D12+D15</f>
         <v>427946</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="16">
         <f>E6+E9+E12+E15</f>
         <v>500517</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="16">
         <f>F6+F9+F12+F15</f>
         <v>516085</v>
       </c>
@@ -3936,7 +3957,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3947,51 +3968,51 @@
       <c r="H1" s="1"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="8" t="s">
         <v>73</v>
       </c>
+      <c r="H3" s="8" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="15">
+      <c r="C4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="11">
         <v>1</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="17">
         <v>55000</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="10">
         <v>0.2</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="10">
         <v>0.0765</v>
       </c>
       <c r="H4" s="18">
@@ -3999,25 +4020,25 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="D5" s="11">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="17">
         <v>45000</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="10">
         <v>0.2</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="10">
         <v>0.0765</v>
       </c>
       <c r="H5" s="18">
@@ -4025,25 +4046,25 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="11">
         <v>0.5</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="17">
         <v>28000</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="10">
         <v>0</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="10">
         <v>0.0765</v>
       </c>
       <c r="H6" s="18">
@@ -4051,126 +4072,126 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="7">
         <v>2.5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>84</v>
+      <c r="A11" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="B11" s="19">
         <v>114000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>85</v>
+      <c r="A12" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="B12" s="19">
         <v>20000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>86</v>
+      <c r="A13" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="B13" s="19">
         <v>8721</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>87</v>
+      <c r="A14" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="B14" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>88</v>
+      <c r="A15" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="B15" s="18">
         <v>142721</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="A17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="A18" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="E18" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F18" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="13">
+      <c r="A19" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="15">
         <v>142721</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="15">
         <v>142721</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="15">
         <v>142721</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="15">
         <v>142721</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="15">
         <v>142721</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>91</v>
+      <c r="A20" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="B20" s="20">
         <f>(1+Assumptions!$B$20)^0</f>
@@ -4194,8 +4215,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>92</v>
+      <c r="A21" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="B21" s="21">
         <f>Assumptions!$B$22</f>
@@ -4215,26 +4236,26 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" s="14">
+      <c r="A22" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="16">
         <f>B19*B20*B21</f>
         <v>118934</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="16">
         <f>C19*C20*C21</f>
         <v>147003</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="16">
         <f>D19*D20*D21</f>
         <v>151413</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="16">
         <f>E19*E20*E21</f>
         <v>155955</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="16">
         <f>F19*F20*F21</f>
         <v>160634</v>
       </c>
@@ -4265,221 +4286,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="15">
         <f>ROUND(Assumptions!$B$17*500,0)</f>
         <v>6000</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <f>ROUND(Assumptions!$C$17*500*(1+Assumptions!$B$21)^1,0)</f>
         <v>9225</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <f>ROUND(Assumptions!$D$17*500*(1+Assumptions!$B$21)^2,0)</f>
         <v>11557</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <f>ROUND(Assumptions!$E$17*500*(1+Assumptions!$B$21)^3,0)</f>
         <v>13461</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <f>ROUND(Assumptions!$F$17*500*(1+Assumptions!$B$21)^4,0)</f>
         <v>13798</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="14">
+      <c r="A4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="16">
         <f>SUM(B3:B3)</f>
         <v>6000</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="16">
         <f>SUM(C3:C3)</f>
         <v>9225</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="16">
         <f>SUM(D3:D3)</f>
         <v>11557</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="16">
         <f>SUM(E3:E3)</f>
         <v>13461</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="16">
         <f>SUM(F3:F3)</f>
         <v>13798</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="A5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="A6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="15">
         <f>ROUND(Assumptions!$B$17*300,0)</f>
         <v>3600</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="15">
         <f>ROUND(Assumptions!$C$17*300*(1+Assumptions!$B$21)^1,0)</f>
         <v>5535</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="15">
         <f>ROUND(Assumptions!$D$17*300*(1+Assumptions!$B$21)^2,0)</f>
         <v>6934</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="15">
         <f>ROUND(Assumptions!$E$17*300*(1+Assumptions!$B$21)^3,0)</f>
         <v>8077</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <f>ROUND(Assumptions!$F$17*300*(1+Assumptions!$B$21)^4,0)</f>
         <v>8279</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="A7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="16">
         <f>SUM(B6:B6)</f>
         <v>3600</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="16">
         <f>SUM(C6:C6)</f>
         <v>5535</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="16">
         <f>SUM(D6:D6)</f>
         <v>6934</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="16">
         <f>SUM(E6:E6)</f>
         <v>8077</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="16">
         <f>SUM(F6:F6)</f>
         <v>8279</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="15">
         <v>3000</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>3075</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>3152</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>3231</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>3311</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="14">
+      <c r="A10" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="16">
         <f>SUM(B9:B9)</f>
         <v>3000</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="16">
         <f>SUM(C9:C9)</f>
         <v>3075</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="16">
         <f>SUM(D9:D9)</f>
         <v>3152</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="16">
         <f>SUM(E9:E9)</f>
         <v>3231</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="16">
         <f>SUM(F9:F9)</f>
         <v>3311</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="14">
+      <c r="A12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="16">
         <f>B4+B7+B10</f>
         <v>12600</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="16">
         <f>C4+C7+C10</f>
         <v>17835</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="16">
         <f>D4+D7+D10</f>
         <v>21643</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="16">
         <f>E4+E7+E10</f>
         <v>24769</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="16">
         <f>F4+F7+F10</f>
         <v>25388</v>
       </c>
@@ -4507,157 +4528,157 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="15">
         <v>30000</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <v>30900</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <v>31827</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <v>32782</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <v>33765</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="15">
         <v>3600</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <v>3690</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <v>3782</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>3877</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>3974</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="15">
         <v>2400</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <v>2460</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="15">
         <v>2522</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="15">
         <v>2585</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <v>2649</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="14">
+      <c r="A6" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="16">
         <f>SUM(B3:B5)</f>
         <v>36000</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="16">
         <f>SUM(C3:C5)</f>
         <v>37050</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="16">
         <f>SUM(D3:D5)</f>
         <v>38131</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="16">
         <f>SUM(E3:E5)</f>
         <v>39244</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="16">
         <f>SUM(F3:F5)</f>
         <v>40388</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="15">
         <v>3000</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="15">
         <v>2058</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="15">
         <v>1733</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="15">
         <v>1570</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>1616</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="14">
         <v>0.19494549648827347</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="14">
         <v>0.10880673808852552</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="14">
         <v>0.08910177919644068</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <v>0.07840507983728856</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="14">
         <v>0.07825870088018447</v>
       </c>
     </row>
@@ -4685,108 +4706,108 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="3"/>
+      <c r="A3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="16">
+      <c r="A4" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" s="16">
+      <c r="A5" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="22">
         <v>30000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="A6" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="23">
         <f>SUM(B4:B5)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="5"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="16">
+      <c r="A9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="22">
         <v>6000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="16">
+      <c r="A10" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="22">
         <v>1800</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B11" s="16">
+      <c r="A11" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="22">
         <v>6000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" s="16">
+      <c r="A12" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="22">
         <v>26572</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="16">
+      <c r="A13" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="22">
         <v>2019</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="22">
+      <c r="A14" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="23">
         <f>SUM(B9:B13)</f>
         <v>42391</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B16" s="23">
+      <c r="A16" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="24">
         <f>B6-B14</f>
         <v>-12391</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
-        <v>124</v>
+      <c r="A17" s="25" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -4818,7 +4839,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4828,134 +4849,134 @@
       <c r="G1" s="1"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>132</v>
       </c>
+      <c r="G3" s="8" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="17">
         <v>30000</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>0.06</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <v>5</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>6960</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>580</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="15">
         <v>4799</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="A6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>135</v>
+      <c r="A7" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="B7" s="18">
         <v>6960</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>136</v>
+      <c r="A8" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="B8" s="19">
         <v>580</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>139</v>
       </c>
+      <c r="B11" s="8" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="13">
+      <c r="A12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="15">
         <v>24840</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="15">
         <v>19371</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="15">
         <v>13573</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="13">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="15">
         <v>7428</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="13">
+      <c r="A16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="15">
         <v>914</v>
       </c>
     </row>
@@ -4986,429 +5007,429 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="M1" s="8" t="s">
         <v>151</v>
       </c>
+      <c r="N1" s="8" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="15">
         <v>155900</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="15">
         <v>7460</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="15">
         <v>7460</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="15">
         <v>7460</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="15">
         <v>7460</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="15">
         <v>7460</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="15">
         <v>7460</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="15">
         <v>7460</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="15">
         <v>7460</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="15">
         <v>-29473</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="15">
         <v>-1440</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="15">
         <v>0</v>
       </c>
-      <c r="N2" s="26">
+      <c r="N2" s="27">
         <f>SUM(B2:M2)</f>
         <v>184667</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="15">
         <v>11893</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <v>11893</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <v>11893</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <v>11893</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <v>11893</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="15">
         <v>11893</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="15">
         <v>11893</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="15">
         <v>11893</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="15">
         <v>11893</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="15">
         <v>11897</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="15">
         <v>0</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="15">
         <v>0</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="15">
         <f>SUM(B3:M3)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="15">
         <v>4050</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <v>4050</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <v>4050</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>4050</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>4050</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="15">
         <v>4050</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="15">
         <v>4050</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="15">
         <v>4050</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="15">
         <v>4050</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="15">
         <v>4050</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="15">
         <v>0</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="15">
         <v>0</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="15">
         <f>SUM(B4:M4)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="15">
         <v>580</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <v>580</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="15">
         <v>580</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="15">
         <v>580</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <v>580</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="15">
         <v>580</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="15">
         <v>580</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="15">
         <v>580</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="15">
         <v>580</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="15">
         <v>580</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="15">
         <v>580</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="15">
         <v>580</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="15">
         <f>SUM(B5:M5)</f>
         <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="A6" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="23">
         <f>SUM(B3:B5)</f>
         <v>16523</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <f>SUM(C3:C5)</f>
         <v>16523</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="23">
         <f>SUM(D3:D5)</f>
         <v>16523</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="23">
         <f>SUM(E3:E5)</f>
         <v>16523</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="23">
         <f>SUM(F3:F5)</f>
         <v>16523</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="23">
         <f>SUM(G3:G5)</f>
         <v>16523</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="23">
         <f>SUM(H3:H5)</f>
         <v>16523</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="23">
         <f>SUM(I3:I5)</f>
         <v>16523</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="23">
         <f>SUM(J3:J5)</f>
         <v>16523</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="23">
         <f>SUM(K3:K5)</f>
         <v>16527</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="23">
         <f>SUM(L3:L5)</f>
         <v>580</v>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="23">
         <f>SUM(M3:M5)</f>
         <v>580</v>
       </c>
-      <c r="N6" s="22">
+      <c r="N6" s="23">
         <f>SUM(B6:M6)</f>
         <v>166394</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" s="26">
+      <c r="A7" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="27">
         <f>B2-B6</f>
         <v>139377</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>C2-C6</f>
         <v>-9063</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>D2-D6</f>
         <v>-9063</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>E2-E6</f>
         <v>-9063</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>F2-F6</f>
         <v>-9063</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>G2-G6</f>
         <v>-9063</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="27">
         <f>H2-H6</f>
         <v>-9063</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <f>I2-I6</f>
         <v>-9063</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="27">
         <f>J2-J6</f>
         <v>-9063</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="27">
         <f>K2-K6</f>
         <v>-46000</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="27">
         <f>L2-L6</f>
         <v>-2020</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="27">
         <f>M2-M6</f>
         <v>-580</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="27">
         <f>SUM(B7:M7)</f>
         <v>18273</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B8" s="26">
+      <c r="A8" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="27">
         <f>30000+B7</f>
         <v>169377</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>B8+C7</f>
         <v>160314</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>C8+D7</f>
         <v>151251</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>D8+E7</f>
         <v>142188</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>E8+F7</f>
         <v>133125</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>F8+G7</f>
         <v>124062</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <f>G8+H7</f>
         <v>114999</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <f>H8+I7</f>
         <v>105936</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="27">
         <f>I8+J7</f>
         <v>96873</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="27">
         <f>J8+K7</f>
         <v>50873</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="27">
         <f>K8+L7</f>
         <v>48853</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="27">
         <f>L8+M7</f>
         <v>48273</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="27">
         <f>M8</f>
         <v>48273</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>160</v>
+      <c r="A11" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="B11" s="19">
         <v>30000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>161</v>
+      <c r="A12" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="B12" s="18">
         <f>M8</f>
@@ -5416,8 +5437,8 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>162</v>
+      <c r="A13" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="B13" s="19">
         <f>MIN(B8:M8)</f>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -19,6 +19,7 @@
     <sheet sheetId="13" name="Underwriting Snapshot" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="Summary" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="Cover" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="Financial Health" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$F23</definedName>
@@ -49,13 +50,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="310">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -829,6 +832,162 @@
   </si>
   <si>
     <t>Summary</t>
+  </si>
+  <si>
+    <t>Bright Horizons Microschool — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>60+ months</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches profit early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
+  </si>
+  <si>
+    <t>Maintain reserves as a buffer against seasonal revenue dips.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 31% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 41.62x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>48.6 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>7 Healthy  |  0 Watch  |  0 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
@@ -844,7 +1003,7 @@
     <numFmt numFmtId="169" formatCode="0.00x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -955,6 +1114,30 @@
     <font>
       <u/>
       <color rgb="FF2563EB"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1071,7 +1254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1130,11 +1313,225 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3330,6 +3727,679 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:H35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="56" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" s="57">
+        <v>12</v>
+      </c>
+      <c r="D7" s="57">
+        <v>18</v>
+      </c>
+      <c r="E7" s="57">
+        <v>22</v>
+      </c>
+      <c r="F7" s="57">
+        <v>25</v>
+      </c>
+      <c r="G7" s="57">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="58">
+        <v>184667</v>
+      </c>
+      <c r="D8" s="58">
+        <v>340512</v>
+      </c>
+      <c r="E8" s="58">
+        <v>427946</v>
+      </c>
+      <c r="F8" s="58">
+        <v>500518</v>
+      </c>
+      <c r="G8" s="58">
+        <v>516085</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="58">
+        <v>118934</v>
+      </c>
+      <c r="D9" s="58">
+        <v>147003</v>
+      </c>
+      <c r="E9" s="58">
+        <v>151413</v>
+      </c>
+      <c r="F9" s="58">
+        <v>155955</v>
+      </c>
+      <c r="G9" s="58">
+        <v>160634</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="58">
+        <v>40500</v>
+      </c>
+      <c r="D10" s="58">
+        <v>54885</v>
+      </c>
+      <c r="E10" s="58">
+        <v>59774</v>
+      </c>
+      <c r="F10" s="58">
+        <v>64012</v>
+      </c>
+      <c r="G10" s="58">
+        <v>65776</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="58">
+        <v>6960</v>
+      </c>
+      <c r="D11" s="58">
+        <v>6960</v>
+      </c>
+      <c r="E11" s="58">
+        <v>6960</v>
+      </c>
+      <c r="F11" s="58">
+        <v>6960</v>
+      </c>
+      <c r="G11" s="58">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="59" t="s">
+        <v>266</v>
+      </c>
+      <c r="C12" s="60">
+        <v>18273</v>
+      </c>
+      <c r="D12" s="60">
+        <v>131665</v>
+      </c>
+      <c r="E12" s="60">
+        <v>209800</v>
+      </c>
+      <c r="F12" s="60">
+        <v>273591</v>
+      </c>
+      <c r="G12" s="60">
+        <v>282716</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="59" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" s="60">
+        <v>48273</v>
+      </c>
+      <c r="D13" s="60">
+        <v>179938</v>
+      </c>
+      <c r="E13" s="60">
+        <v>389738</v>
+      </c>
+      <c r="F13" s="60">
+        <v>663329</v>
+      </c>
+      <c r="G13" s="60">
+        <v>946045</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="59" t="s">
+        <v>268</v>
+      </c>
+      <c r="C14" s="61">
+        <v>0.09895108492583948</v>
+      </c>
+      <c r="D14" s="61">
+        <v>0.38666772389812987</v>
+      </c>
+      <c r="E14" s="61">
+        <v>0.4902487697045889</v>
+      </c>
+      <c r="F14" s="61">
+        <v>0.5466157061284509</v>
+      </c>
+      <c r="G14" s="61">
+        <v>0.5478089849540289</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="62">
+        <v>15388.916666666666</v>
+      </c>
+      <c r="D15" s="62">
+        <v>18917.333333333332</v>
+      </c>
+      <c r="E15" s="62">
+        <v>19452.090909090908</v>
+      </c>
+      <c r="F15" s="62">
+        <v>20020.72</v>
+      </c>
+      <c r="G15" s="62">
+        <v>20643.4</v>
+      </c>
+      <c r="H15" s="63" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="59" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" s="64">
+        <v>0.6440457688704533</v>
+      </c>
+      <c r="D16" s="61">
+        <v>0.43171165773893433</v>
+      </c>
+      <c r="E16" s="61">
+        <v>0.3538133315885649</v>
+      </c>
+      <c r="F16" s="61">
+        <v>0.31158719566529075</v>
+      </c>
+      <c r="G16" s="61">
+        <v>0.3112549289361249</v>
+      </c>
+      <c r="H16" s="63" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="59" t="s">
+        <v>272</v>
+      </c>
+      <c r="C17" s="61">
+        <v>0.0657941050647923</v>
+      </c>
+      <c r="D17" s="61">
+        <v>0.04835512404849168</v>
+      </c>
+      <c r="E17" s="61">
+        <v>0.04190295037224323</v>
+      </c>
+      <c r="F17" s="61">
+        <v>0.03836745132043203</v>
+      </c>
+      <c r="G17" s="61">
+        <v>0.038235561971380685</v>
+      </c>
+      <c r="H17" s="63" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="59" t="s">
+        <v>274</v>
+      </c>
+      <c r="C18" s="61">
+        <v>0.13664054758023902</v>
+      </c>
+      <c r="D18" s="61">
+        <v>0.40710459543276006</v>
+      </c>
+      <c r="E18" s="61">
+        <v>0.5065101671706244</v>
+      </c>
+      <c r="F18" s="61">
+        <v>0.5605212999332692</v>
+      </c>
+      <c r="G18" s="61">
+        <v>0.5612931978259396</v>
+      </c>
+      <c r="H18" s="63" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="59" t="s">
+        <v>276</v>
+      </c>
+      <c r="C19" s="65">
+        <v>1</v>
+      </c>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="63" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="59" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="66">
+        <v>3.6254310344827587</v>
+      </c>
+      <c r="D20" s="66">
+        <v>19.917241379310344</v>
+      </c>
+      <c r="E20" s="66">
+        <v>31.14353448275862</v>
+      </c>
+      <c r="F20" s="66">
+        <v>40.30905172413793</v>
+      </c>
+      <c r="G20" s="66">
+        <v>41.61997126436781</v>
+      </c>
+      <c r="H20" s="63" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="59" t="s">
+        <v>279</v>
+      </c>
+      <c r="C21" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="63" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="59" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="63" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="D25" s="70" t="s">
+        <v>288</v>
+      </c>
+      <c r="E25" s="70"/>
+      <c r="F25" s="71" t="s">
+        <v>289</v>
+      </c>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="C26" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="D26" s="70" t="s">
+        <v>291</v>
+      </c>
+      <c r="E26" s="70"/>
+      <c r="F26" s="71" t="s">
+        <v>292</v>
+      </c>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="68" t="s">
+        <v>293</v>
+      </c>
+      <c r="C27" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="D27" s="70" t="s">
+        <v>294</v>
+      </c>
+      <c r="E27" s="70"/>
+      <c r="F27" s="71" t="s">
+        <v>295</v>
+      </c>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="68" t="s">
+        <v>296</v>
+      </c>
+      <c r="C28" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="D28" s="70" t="s">
+        <v>297</v>
+      </c>
+      <c r="E28" s="70"/>
+      <c r="F28" s="71" t="s">
+        <v>298</v>
+      </c>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="68" t="s">
+        <v>299</v>
+      </c>
+      <c r="C29" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="D29" s="70" t="s">
+        <v>300</v>
+      </c>
+      <c r="E29" s="70"/>
+      <c r="F29" s="71" t="s">
+        <v>301</v>
+      </c>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="C30" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>303</v>
+      </c>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="C31" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="D31" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="E31" s="70"/>
+      <c r="F31" s="71" t="s">
+        <v>307</v>
+      </c>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="68" t="s">
+        <v>257</v>
+      </c>
+      <c r="C33" s="59" t="s">
+        <v>308</v>
+      </c>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="72" t="s">
+        <v>309</v>
+      </c>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C14&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C14&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C14&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&gt;=10000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&gt;=7000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&lt;7000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BBright Horizons Microschool&amp;R&amp;8&amp;IFinancial Health</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -40,7 +40,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Debt Schedule'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Cash Flow Monthly Y1'!$A1:$N13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Cash Flow Monthly Y1'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'5-Year P&amp;L'!$A1:$F9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'5-Year P&amp;L'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'5-Year P&amp;L'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'5-Year Balance Sheet'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'5-Year Balance Sheet'!$1:$1</definedName>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="312">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -565,6 +565,12 @@
   </si>
   <si>
     <t>Cumulative Net Income</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>ASSETS</t>
@@ -1057,6 +1063,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF1E293B"/>
       <sz val="16"/>
       <name val="Calibri"/>
@@ -1120,12 +1132,6 @@
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1254,7 +1260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1287,6 +1293,12 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1296,25 +1308,25 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1336,26 +1348,23 @@
     <xf numFmtId="166" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2100,7 +2109,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -2320,6 +2329,26 @@
       <c r="F9" s="27">
         <f>E9+F7</f>
         <v>916045</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2366,7 +2395,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2376,7 +2405,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B3" s="15">
         <v>48273</v>
@@ -2396,7 +2425,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B4" s="15">
         <v>0</v>
@@ -2416,7 +2445,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B5" s="16">
         <f>SUM(B3:B4)</f>
@@ -2441,7 +2470,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -2451,7 +2480,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B8" s="15">
         <v>24840</v>
@@ -2471,7 +2500,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B9" s="15">
         <v>0</v>
@@ -2491,7 +2520,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B10" s="16">
         <f>SUM(B8:B9)</f>
@@ -2516,7 +2545,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2526,7 +2555,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B13" s="15">
         <v>0</v>
@@ -2546,7 +2575,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B14" s="15">
         <v>23433</v>
@@ -2566,7 +2595,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" s="16">
         <f>B5-B10</f>
@@ -2591,7 +2620,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B17" s="27" t="str">
         <f>B5-B10-B15</f>
@@ -2658,7 +2687,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2668,7 +2697,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B3" s="15">
         <v>25233</v>
@@ -2708,32 +2737,32 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="30">
+        <v>186</v>
+      </c>
+      <c r="B5" s="32">
         <f>IF(B4=0,"N/A",B3/B4)</f>
         <v>3.63</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="32">
         <f>IF(C4=0,"N/A",C3/C4)</f>
         <v>19.92</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="32">
         <f>IF(D4=0,"N/A",D3/D4)</f>
         <v>31.14</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="32">
         <f>IF(E4=0,"N/A",E3/E4)</f>
         <v>40.31</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="32">
         <f>IF(F4=0,"N/A",F3/F4)</f>
         <v>41.62</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -2743,7 +2772,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B8" s="15">
         <v>48273</v>
@@ -2763,7 +2792,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B9" s="15">
         <v>13286</v>
@@ -2783,52 +2812,52 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="B10" s="31">
+        <v>190</v>
+      </c>
+      <c r="B10" s="33">
         <f>IF(B9=0,0,B8/B9)</f>
         <v>3.63</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="33">
         <f>IF(C9=0,0,C8/C9)</f>
         <v>10.7</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="33">
         <f>IF(D9=0,0,D8/D9)</f>
         <v>22.15</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="33">
         <f>IF(E9=0,0,E8/E9)</f>
         <v>36.19</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="33">
         <f>IF(F9=0,0,F8/F9)</f>
         <v>50.14</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="B11" s="32">
+        <v>191</v>
+      </c>
+      <c r="B11" s="34">
         <v>111</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="34">
         <v>325</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="34">
         <v>674</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="34">
         <v>1101</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="34">
         <v>1525</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -2838,92 +2867,92 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B14" s="33" t="str">
+        <v>193</v>
+      </c>
+      <c r="B14" s="35" t="str">
         <f>IF(B5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C14" s="33" t="str">
+      <c r="C14" s="35" t="str">
         <f>IF(C5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D14" s="33" t="str">
+      <c r="D14" s="35" t="str">
         <f>IF(D5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E14" s="33" t="str">
+      <c r="E14" s="35" t="str">
         <f>IF(E5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F14" s="33" t="str">
+      <c r="F14" s="35" t="str">
         <f>IF(F5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="33" t="str">
+        <v>194</v>
+      </c>
+      <c r="B15" s="35" t="str">
         <f>IF(B10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C15" s="33" t="str">
+      <c r="C15" s="35" t="str">
         <f>IF(C10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D15" s="33" t="str">
+      <c r="D15" s="35" t="str">
         <f>IF(D10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E15" s="33" t="str">
+      <c r="E15" s="35" t="str">
         <f>IF(E10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F15" s="33" t="str">
+      <c r="F15" s="35" t="str">
         <f>IF(F10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>194</v>
+        <v>195</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="B17" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>196</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>194</v>
+      <c r="D17" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2950,65 +2979,65 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
+      <c r="A1" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
+      <c r="A2" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>194</v>
+        <v>202</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>196</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>194</v>
+        <v>204</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>196</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>194</v>
+        <v>206</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>196</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>194</v>
+        <v>208</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>196</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>35</v>
@@ -3016,59 +3045,59 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>196</v>
+        <v>209</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>198</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>194</v>
+        <v>211</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>196</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>214</v>
+        <v>215</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B17" s="18">
         <v>184667</v>
@@ -3076,7 +3105,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B18" s="18">
         <v>166394</v>
@@ -3084,7 +3113,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" s="18">
         <v>18273</v>
@@ -3092,9 +3121,9 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B20" s="38">
+        <v>221</v>
+      </c>
+      <c r="B20" s="40">
         <v>0.09895108492583948</v>
       </c>
     </row>
@@ -3108,7 +3137,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B22" s="18">
         <v>48273</v>
@@ -3116,7 +3145,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B23" s="18">
         <v>30000</v>
@@ -3124,23 +3153,23 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>35</v>
@@ -3148,7 +3177,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B27" s="18">
         <v>15389</v>
@@ -3156,7 +3185,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B28" s="18">
         <v>13866</v>
@@ -3189,44 +3218,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="A2" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="A3" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
     </row>
     <row r="4" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
+      <c r="A4" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -3252,23 +3281,23 @@
       <c r="A7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="34">
         <f>Assumptions!$B$17</f>
         <v>12</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="34">
         <f>Assumptions!$C$17</f>
         <v>18</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="34">
         <f>Assumptions!$D$17</f>
         <v>22</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="34">
         <f>Assumptions!$E$17</f>
         <v>25</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="34">
         <f>Assumptions!$F$17</f>
         <v>25</v>
       </c>
@@ -3400,7 +3429,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B13" s="27">
         <v>48273</v>
@@ -3420,7 +3449,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B14" s="15">
         <v>15389</v>
@@ -3460,33 +3489,33 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B16" s="30">
+        <v>186</v>
+      </c>
+      <c r="B16" s="32">
         <v>3.63</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="32">
         <v>19.92</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="32">
         <v>31.14</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="32">
         <v>40.31</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="32">
         <v>41.62</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
-        <v>233</v>
-      </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
+      <c r="A18" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3522,56 +3551,56 @@
     <row r="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
-        <v>234</v>
-      </c>
-      <c r="C3" s="42"/>
+      <c r="B3" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="C4" s="43"/>
+      <c r="B4" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="45"/>
     </row>
     <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="45" t="s">
-        <v>236</v>
+      <c r="B8" s="47" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="46"/>
+      <c r="C9" s="48"/>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="C10" s="47"/>
+      <c r="B10" s="49" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="49"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>239</v>
+      <c r="B12" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C16" s="27">
         <v>516085</v>
@@ -3579,7 +3608,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C17" s="27">
         <v>282716</v>
@@ -3587,7 +3616,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C18" s="27">
         <v>916045</v>
@@ -3595,108 +3624,108 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>243</v>
+        <v>215</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="5"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="C23" s="51"/>
+      <c r="B23" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="C23" s="53"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="50" t="s">
-        <v>246</v>
-      </c>
-      <c r="C24" s="51"/>
+      <c r="B24" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" s="53"/>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="50" t="s">
-        <v>247</v>
-      </c>
-      <c r="C25" s="51"/>
+      <c r="B25" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="C25" s="53"/>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="C26" s="51"/>
+      <c r="B26" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="C26" s="53"/>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="50" t="s">
+      <c r="B27" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="C27" s="51"/>
+      <c r="C27" s="53"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="51"/>
+      <c r="B28" s="52" t="s">
+        <v>251</v>
+      </c>
+      <c r="C28" s="53"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="50" t="s">
-        <v>250</v>
-      </c>
-      <c r="C29" s="51"/>
+      <c r="B29" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="C29" s="53"/>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="50" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="51"/>
+      <c r="B30" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="C30" s="53"/>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="C31" s="51"/>
+      <c r="B31" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="C31" s="53"/>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="50" t="s">
-        <v>253</v>
-      </c>
-      <c r="C32" s="51"/>
+      <c r="B32" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="C32" s="53"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="s">
-        <v>254</v>
-      </c>
-      <c r="C33" s="51"/>
+      <c r="B33" s="52" t="s">
+        <v>256</v>
+      </c>
+      <c r="C33" s="53"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="50" t="s">
-        <v>255</v>
-      </c>
-      <c r="C34" s="51"/>
+      <c r="B34" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C34" s="53"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="C35" s="51"/>
+      <c r="B35" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="C35" s="53"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="50" t="s">
-        <v>257</v>
-      </c>
-      <c r="C36" s="51"/>
+      <c r="B36" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="C36" s="53"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="41" t="s">
-        <v>233</v>
-      </c>
-      <c r="C39" s="41"/>
+      <c r="B39" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="C39" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3744,78 +3773,78 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="52" t="s">
-        <v>259</v>
-      </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="B3" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="53" t="s">
-        <v>260</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>261</v>
-      </c>
-      <c r="F4" s="55" t="s">
+      <c r="B4" s="55" t="s">
         <v>262</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>263</v>
+      </c>
+      <c r="F4" s="57" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C6" s="56" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="56" t="s">
+      <c r="G6" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="56" t="s">
-        <v>264</v>
+      <c r="H6" s="58" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="C7" s="57">
+        <v>267</v>
+      </c>
+      <c r="C7" s="59">
         <v>12</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="59">
         <v>18</v>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="59">
         <v>22</v>
       </c>
-      <c r="F7" s="57">
+      <c r="F7" s="59">
         <v>25</v>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="59">
         <v>25</v>
       </c>
     </row>
@@ -3823,19 +3852,19 @@
       <c r="B8" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="58">
+      <c r="C8" s="60">
         <v>184667</v>
       </c>
-      <c r="D8" s="58">
+      <c r="D8" s="60">
         <v>340512</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="60">
         <v>427946</v>
       </c>
-      <c r="F8" s="58">
+      <c r="F8" s="60">
         <v>500518</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8" s="60">
         <v>516085</v>
       </c>
     </row>
@@ -3843,19 +3872,19 @@
       <c r="B9" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="58">
+      <c r="C9" s="60">
         <v>118934</v>
       </c>
-      <c r="D9" s="58">
+      <c r="D9" s="60">
         <v>147003</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="60">
         <v>151413</v>
       </c>
-      <c r="F9" s="58">
+      <c r="F9" s="60">
         <v>155955</v>
       </c>
-      <c r="G9" s="58">
+      <c r="G9" s="60">
         <v>160634</v>
       </c>
     </row>
@@ -3863,19 +3892,19 @@
       <c r="B10" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="58">
+      <c r="C10" s="60">
         <v>40500</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="60">
         <v>54885</v>
       </c>
-      <c r="E10" s="58">
+      <c r="E10" s="60">
         <v>59774</v>
       </c>
-      <c r="F10" s="58">
+      <c r="F10" s="60">
         <v>64012</v>
       </c>
-      <c r="G10" s="58">
+      <c r="G10" s="60">
         <v>65776</v>
       </c>
     </row>
@@ -3883,399 +3912,399 @@
       <c r="B11" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="60">
         <v>6960</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="60">
         <v>6960</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="60">
         <v>6960</v>
       </c>
-      <c r="F11" s="58">
+      <c r="F11" s="60">
         <v>6960</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11" s="60">
         <v>6960</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="59" t="s">
-        <v>266</v>
-      </c>
-      <c r="C12" s="60">
+      <c r="B12" s="61" t="s">
+        <v>268</v>
+      </c>
+      <c r="C12" s="62">
         <v>18273</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="62">
         <v>131665</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E12" s="62">
         <v>209800</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F12" s="62">
         <v>273591</v>
       </c>
-      <c r="G12" s="60">
+      <c r="G12" s="62">
         <v>282716</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="59" t="s">
-        <v>267</v>
-      </c>
-      <c r="C13" s="60">
+      <c r="B13" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" s="62">
         <v>48273</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="62">
         <v>179938</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="62">
         <v>389738</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F13" s="62">
         <v>663329</v>
       </c>
-      <c r="G13" s="60">
+      <c r="G13" s="62">
         <v>946045</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="59" t="s">
-        <v>268</v>
-      </c>
-      <c r="C14" s="61">
+      <c r="B14" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="C14" s="63">
         <v>0.09895108492583948</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="63">
         <v>0.38666772389812987</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="63">
         <v>0.4902487697045889</v>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="63">
         <v>0.5466157061284509</v>
       </c>
-      <c r="G14" s="61">
+      <c r="G14" s="63">
         <v>0.5478089849540289</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="59" t="s">
-        <v>232</v>
-      </c>
-      <c r="C15" s="62">
+      <c r="B15" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="64">
         <v>15388.916666666666</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="64">
         <v>18917.333333333332</v>
       </c>
-      <c r="E15" s="62">
+      <c r="E15" s="64">
         <v>19452.090909090908</v>
       </c>
-      <c r="F15" s="62">
+      <c r="F15" s="64">
         <v>20020.72</v>
       </c>
-      <c r="G15" s="62">
+      <c r="G15" s="64">
         <v>20643.4</v>
       </c>
-      <c r="H15" s="63" t="s">
-        <v>269</v>
+      <c r="H15" s="65" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="59" t="s">
-        <v>270</v>
-      </c>
-      <c r="C16" s="64">
+      <c r="B16" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="C16" s="66">
         <v>0.6440457688704533</v>
       </c>
-      <c r="D16" s="61">
+      <c r="D16" s="63">
         <v>0.43171165773893433</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="63">
         <v>0.3538133315885649</v>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="63">
         <v>0.31158719566529075</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G16" s="63">
         <v>0.3112549289361249</v>
       </c>
-      <c r="H16" s="63" t="s">
-        <v>271</v>
+      <c r="H16" s="65" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="59" t="s">
-        <v>272</v>
-      </c>
-      <c r="C17" s="61">
+      <c r="B17" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="63">
         <v>0.0657941050647923</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="63">
         <v>0.04835512404849168</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="63">
         <v>0.04190295037224323</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="63">
         <v>0.03836745132043203</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="63">
         <v>0.038235561971380685</v>
       </c>
-      <c r="H17" s="63" t="s">
-        <v>273</v>
+      <c r="H17" s="65" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="59" t="s">
-        <v>274</v>
-      </c>
-      <c r="C18" s="61">
+      <c r="B18" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="63">
         <v>0.13664054758023902</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D18" s="63">
         <v>0.40710459543276006</v>
       </c>
-      <c r="E18" s="61">
+      <c r="E18" s="63">
         <v>0.5065101671706244</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="63">
         <v>0.5605212999332692</v>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="63">
         <v>0.5612931978259396</v>
       </c>
-      <c r="H18" s="63" t="s">
-        <v>275</v>
+      <c r="H18" s="65" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="59" t="s">
-        <v>276</v>
-      </c>
-      <c r="C19" s="65">
-        <v>1</v>
-      </c>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="63" t="s">
-        <v>277</v>
+      <c r="B19" s="61" t="s">
+        <v>278</v>
+      </c>
+      <c r="C19" s="67">
+        <v>3</v>
+      </c>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="65" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="59" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="66">
+      <c r="B20" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" s="68">
         <v>3.6254310344827587</v>
       </c>
-      <c r="D20" s="66">
+      <c r="D20" s="68">
         <v>19.917241379310344</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="68">
         <v>31.14353448275862</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="68">
         <v>40.30905172413793</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G20" s="68">
         <v>41.61997126436781</v>
       </c>
-      <c r="H20" s="63" t="s">
-        <v>278</v>
+      <c r="H20" s="65" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="59" t="s">
-        <v>279</v>
-      </c>
-      <c r="C21" s="67" t="s">
+      <c r="B21" s="61" t="s">
+        <v>281</v>
+      </c>
+      <c r="C21" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="63" t="s">
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="65" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="59" t="s">
-        <v>280</v>
-      </c>
-      <c r="C22" s="67" t="s">
-        <v>281</v>
-      </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="63" t="s">
-        <v>281</v>
+      <c r="B22" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="C22" s="69" t="s">
+        <v>283</v>
+      </c>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="65" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="68" t="s">
-        <v>286</v>
-      </c>
-      <c r="C25" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="D25" s="70" t="s">
+      <c r="B25" s="70" t="s">
         <v>288</v>
       </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71" t="s">
+      <c r="C25" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
+      <c r="D25" s="71" t="s">
+        <v>290</v>
+      </c>
+      <c r="E25" s="71"/>
+      <c r="F25" s="72" t="s">
+        <v>291</v>
+      </c>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="68" t="s">
-        <v>290</v>
-      </c>
-      <c r="C26" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="D26" s="70" t="s">
-        <v>291</v>
-      </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71" t="s">
+      <c r="B26" s="70" t="s">
         <v>292</v>
       </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
+      <c r="C26" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D26" s="71" t="s">
+        <v>293</v>
+      </c>
+      <c r="E26" s="71"/>
+      <c r="F26" s="72" t="s">
+        <v>294</v>
+      </c>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="68" t="s">
-        <v>293</v>
-      </c>
-      <c r="C27" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="D27" s="70" t="s">
-        <v>294</v>
-      </c>
-      <c r="E27" s="70"/>
-      <c r="F27" s="71" t="s">
+      <c r="B27" s="70" t="s">
         <v>295</v>
       </c>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
+      <c r="C27" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D27" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="E27" s="71"/>
+      <c r="F27" s="72" t="s">
+        <v>297</v>
+      </c>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="68" t="s">
-        <v>296</v>
-      </c>
-      <c r="C28" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="D28" s="70" t="s">
-        <v>297</v>
-      </c>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71" t="s">
+      <c r="B28" s="70" t="s">
         <v>298</v>
       </c>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
+      <c r="C28" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="E28" s="71"/>
+      <c r="F28" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="68" t="s">
-        <v>299</v>
-      </c>
-      <c r="C29" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="D29" s="70" t="s">
-        <v>300</v>
-      </c>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71" t="s">
+      <c r="B29" s="70" t="s">
         <v>301</v>
       </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
+      <c r="C29" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D29" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="E29" s="71"/>
+      <c r="F29" s="72" t="s">
+        <v>303</v>
+      </c>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="68" t="s">
-        <v>302</v>
-      </c>
-      <c r="C30" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="D30" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71" t="s">
+      <c r="B30" s="70" t="s">
         <v>304</v>
       </c>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
+      <c r="C30" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D30" s="71" t="s">
+        <v>305</v>
+      </c>
+      <c r="E30" s="71"/>
+      <c r="F30" s="72" t="s">
+        <v>306</v>
+      </c>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="68" t="s">
-        <v>305</v>
-      </c>
-      <c r="C31" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="D31" s="70" t="s">
-        <v>306</v>
-      </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="71" t="s">
+      <c r="B31" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
+      <c r="C31" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" s="71" t="s">
+        <v>308</v>
+      </c>
+      <c r="E31" s="71"/>
+      <c r="F31" s="72" t="s">
+        <v>309</v>
+      </c>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="68" t="s">
-        <v>257</v>
-      </c>
-      <c r="C33" s="59" t="s">
-        <v>308</v>
-      </c>
-      <c r="D33" s="59"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="59"/>
+      <c r="B33" s="70" t="s">
+        <v>259</v>
+      </c>
+      <c r="C33" s="61" t="s">
+        <v>310</v>
+      </c>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="72" t="s">
-        <v>309</v>
-      </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
+      <c r="B35" s="73" t="s">
+        <v>311</v>
+      </c>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -4414,10 +4414,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="312">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -1260,7 +1260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1355,6 +1355,9 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4122,13 +4125,26 @@
       <c r="B21" s="61" t="s">
         <v>281</v>
       </c>
-      <c r="C21" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
+      <c r="C21" s="30" t="str">
+        <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="69" t="str">
+        <f>IF('5-Year P&amp;L'!C9&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="69" t="str">
+        <f>IF('5-Year P&amp;L'!D9&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="69" t="str">
+        <f>IF('5-Year P&amp;L'!E9&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="69" t="str">
+        <f>IF('5-Year P&amp;L'!F9&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="65" t="s">
         <v>23</v>
       </c>
@@ -4137,13 +4153,13 @@
       <c r="B22" s="61" t="s">
         <v>282</v>
       </c>
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="70" t="s">
         <v>283</v>
       </c>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
       <c r="H22" s="65" t="s">
         <v>283</v>
       </c>
@@ -4166,126 +4182,126 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="71" t="s">
         <v>288</v>
       </c>
       <c r="C25" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="D25" s="72" t="s">
         <v>290</v>
       </c>
-      <c r="E25" s="71"/>
-      <c r="F25" s="72" t="s">
+      <c r="E25" s="72"/>
+      <c r="F25" s="73" t="s">
         <v>291</v>
       </c>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="71" t="s">
         <v>292</v>
       </c>
       <c r="C26" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="72" t="s">
         <v>293</v>
       </c>
-      <c r="E26" s="71"/>
-      <c r="F26" s="72" t="s">
+      <c r="E26" s="72"/>
+      <c r="F26" s="73" t="s">
         <v>294</v>
       </c>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="70" t="s">
+      <c r="B27" s="71" t="s">
         <v>295</v>
       </c>
       <c r="C27" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D27" s="71" t="s">
+      <c r="D27" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="E27" s="71"/>
-      <c r="F27" s="72" t="s">
+      <c r="E27" s="72"/>
+      <c r="F27" s="73" t="s">
         <v>297</v>
       </c>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="70" t="s">
+      <c r="B28" s="71" t="s">
         <v>298</v>
       </c>
       <c r="C28" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="72" t="s">
         <v>299</v>
       </c>
-      <c r="E28" s="71"/>
-      <c r="F28" s="72" t="s">
+      <c r="E28" s="72"/>
+      <c r="F28" s="73" t="s">
         <v>300</v>
       </c>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="70" t="s">
+      <c r="B29" s="71" t="s">
         <v>301</v>
       </c>
       <c r="C29" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="72" t="s">
         <v>302</v>
       </c>
-      <c r="E29" s="71"/>
-      <c r="F29" s="72" t="s">
+      <c r="E29" s="72"/>
+      <c r="F29" s="73" t="s">
         <v>303</v>
       </c>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="70" t="s">
+      <c r="B30" s="71" t="s">
         <v>304</v>
       </c>
       <c r="C30" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D30" s="71" t="s">
+      <c r="D30" s="72" t="s">
         <v>305</v>
       </c>
-      <c r="E30" s="71"/>
-      <c r="F30" s="72" t="s">
+      <c r="E30" s="72"/>
+      <c r="F30" s="73" t="s">
         <v>306</v>
       </c>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="70" t="s">
+      <c r="B31" s="71" t="s">
         <v>307</v>
       </c>
       <c r="C31" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D31" s="71" t="s">
+      <c r="D31" s="72" t="s">
         <v>308</v>
       </c>
-      <c r="E31" s="71"/>
-      <c r="F31" s="72" t="s">
+      <c r="E31" s="72"/>
+      <c r="F31" s="73" t="s">
         <v>309</v>
       </c>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="71" t="s">
         <v>259</v>
       </c>
       <c r="C33" s="61" t="s">
@@ -4296,22 +4312,21 @@
       <c r="F33" s="61"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="73" t="s">
+      <c r="B35" s="74" t="s">
         <v>311</v>
       </c>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -4392,10 +4407,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="312">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -906,10 +906,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1260,7 +1260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1352,14 +1352,21 @@
     <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="169" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4090,10 +4097,18 @@
       <c r="C19" s="67">
         <v>3</v>
       </c>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
+      <c r="D19" s="67">
+        <v>3</v>
+      </c>
+      <c r="E19" s="67">
+        <v>3</v>
+      </c>
+      <c r="F19" s="67">
+        <v>3</v>
+      </c>
+      <c r="G19" s="67">
+        <v>3</v>
+      </c>
       <c r="H19" s="65" t="s">
         <v>279</v>
       </c>
@@ -4130,19 +4145,19 @@
         <v>✓ Break-even</v>
       </c>
       <c r="D21" s="69" t="str">
-        <f>IF('5-Year P&amp;L'!C9&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="69" t="str">
-        <f>IF('5-Year P&amp;L'!D9&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="69" t="str">
-        <f>IF('5-Year P&amp;L'!E9&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="69" t="str">
-        <f>IF('5-Year P&amp;L'!F9&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="65" t="s">
@@ -4153,13 +4168,21 @@
       <c r="B22" s="61" t="s">
         <v>282</v>
       </c>
-      <c r="C22" s="70" t="s">
-        <v>283</v>
-      </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
+      <c r="C22" s="70">
+        <v>3</v>
+      </c>
+      <c r="D22" s="70">
+        <v>10</v>
+      </c>
+      <c r="E22" s="71">
+        <v>21</v>
+      </c>
+      <c r="F22" s="67">
+        <v>35</v>
+      </c>
+      <c r="G22" s="67">
+        <v>49</v>
+      </c>
       <c r="H22" s="65" t="s">
         <v>283</v>
       </c>
@@ -4182,126 +4205,126 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="71" t="s">
+      <c r="B25" s="72" t="s">
         <v>288</v>
       </c>
       <c r="C25" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D25" s="72" t="s">
+      <c r="D25" s="73" t="s">
         <v>290</v>
       </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73" t="s">
+      <c r="E25" s="73"/>
+      <c r="F25" s="74" t="s">
         <v>291</v>
       </c>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="71" t="s">
+      <c r="B26" s="72" t="s">
         <v>292</v>
       </c>
       <c r="C26" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D26" s="72" t="s">
+      <c r="D26" s="73" t="s">
         <v>293</v>
       </c>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73" t="s">
+      <c r="E26" s="73"/>
+      <c r="F26" s="74" t="s">
         <v>294</v>
       </c>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="71" t="s">
+      <c r="B27" s="72" t="s">
         <v>295</v>
       </c>
       <c r="C27" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D27" s="72" t="s">
+      <c r="D27" s="73" t="s">
         <v>296</v>
       </c>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73" t="s">
+      <c r="E27" s="73"/>
+      <c r="F27" s="74" t="s">
         <v>297</v>
       </c>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="71" t="s">
+      <c r="B28" s="72" t="s">
         <v>298</v>
       </c>
       <c r="C28" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D28" s="72" t="s">
+      <c r="D28" s="73" t="s">
         <v>299</v>
       </c>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73" t="s">
+      <c r="E28" s="73"/>
+      <c r="F28" s="74" t="s">
         <v>300</v>
       </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="72" t="s">
         <v>301</v>
       </c>
       <c r="C29" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D29" s="72" t="s">
+      <c r="D29" s="73" t="s">
         <v>302</v>
       </c>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73" t="s">
+      <c r="E29" s="73"/>
+      <c r="F29" s="74" t="s">
         <v>303</v>
       </c>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="71" t="s">
+      <c r="B30" s="72" t="s">
         <v>304</v>
       </c>
       <c r="C30" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D30" s="72" t="s">
+      <c r="D30" s="73" t="s">
         <v>305</v>
       </c>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73" t="s">
+      <c r="E30" s="73"/>
+      <c r="F30" s="74" t="s">
         <v>306</v>
       </c>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="71" t="s">
+      <c r="B31" s="72" t="s">
         <v>307</v>
       </c>
       <c r="C31" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D31" s="72" t="s">
+      <c r="D31" s="73" t="s">
         <v>308</v>
       </c>
-      <c r="E31" s="72"/>
-      <c r="F31" s="73" t="s">
+      <c r="E31" s="73"/>
+      <c r="F31" s="74" t="s">
         <v>309</v>
       </c>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="71" t="s">
+      <c r="B33" s="72" t="s">
         <v>259</v>
       </c>
       <c r="C33" s="61" t="s">
@@ -4312,22 +4335,20 @@
       <c r="F33" s="61"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="74" t="s">
+      <c r="B35" s="75" t="s">
         <v>311</v>
       </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -957,7 +957,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 8% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -4048,20 +4048,20 @@
       <c r="B17" s="61" t="s">
         <v>274</v>
       </c>
-      <c r="C17" s="63">
-        <v>0.0657941050647923</v>
+      <c r="C17" s="66">
+        <v>0.19494549648827347</v>
       </c>
       <c r="D17" s="63">
-        <v>0.04835512404849168</v>
+        <v>0.10880673808852552</v>
       </c>
       <c r="E17" s="63">
-        <v>0.04190295037224323</v>
+        <v>0.08910177919644068</v>
       </c>
       <c r="F17" s="63">
-        <v>0.03836745132043203</v>
+        <v>0.07840507983728856</v>
       </c>
       <c r="G17" s="63">
-        <v>0.038235561971380685</v>
+        <v>0.07825870088018447</v>
       </c>
       <c r="H17" s="65" t="s">
         <v>275</v>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -756,7 +756,7 @@
     <t>Microschool  |  AZ  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 26, 2026</t>
+    <t>Prepared March 27, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -783,7 +783,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>
@@ -843,7 +843,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="313">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -910,6 +910,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -3772,7 +3775,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4187,170 +4190,191 @@
         <v>283</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" s="67">
+        <v>106</v>
+      </c>
+      <c r="D23" s="67">
+        <v>314</v>
+      </c>
+      <c r="E23" s="67">
+        <v>652</v>
+      </c>
+      <c r="F23" s="67">
+        <v>1067</v>
+      </c>
+      <c r="G23" s="67">
+        <v>1480</v>
+      </c>
+      <c r="H23" s="65" t="s">
         <v>284</v>
       </c>
-      <c r="C24" s="5" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="72" t="s">
+      <c r="E25" s="5"/>
+      <c r="F25" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C25" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D25" s="73" t="s">
-        <v>290</v>
-      </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74" t="s">
-        <v>291</v>
-      </c>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="72" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D26" s="73" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E26" s="73"/>
       <c r="F26" s="74" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G26" s="74"/>
       <c r="H26" s="74"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="72" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D27" s="73" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E27" s="73"/>
       <c r="F27" s="74" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G27" s="74"/>
       <c r="H27" s="74"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="72" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D28" s="73" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E28" s="73"/>
       <c r="F28" s="74" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G28" s="74"/>
       <c r="H28" s="74"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="72" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D29" s="73" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E29" s="73"/>
       <c r="F29" s="74" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G29" s="74"/>
       <c r="H29" s="74"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="72" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D30" s="73" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E30" s="73"/>
       <c r="F30" s="74" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G30" s="74"/>
       <c r="H30" s="74"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="72" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D31" s="73" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E31" s="73"/>
       <c r="F31" s="74" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G31" s="74"/>
       <c r="H31" s="74"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="72" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="72" t="s">
+        <v>308</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" s="73" t="s">
+        <v>309</v>
+      </c>
+      <c r="E32" s="73"/>
+      <c r="F32" s="74" t="s">
+        <v>310</v>
+      </c>
+      <c r="G32" s="74"/>
+      <c r="H32" s="74"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="72" t="s">
         <v>259</v>
       </c>
-      <c r="C33" s="61" t="s">
-        <v>310</v>
-      </c>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="75" t="s">
+      <c r="C34" s="61" t="s">
         <v>311</v>
       </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="75" t="s">
+        <v>312</v>
+      </c>
+      <c r="C36" s="75"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -4365,8 +4389,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="317">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -874,6 +874,18 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1263,7 +1275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1352,6 +1364,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3775,7 +3796,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4024,365 +4045,440 @@
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="66">
+        <v>13866.166666666666</v>
+      </c>
+      <c r="D16" s="66">
+        <v>11602.666666666666</v>
+      </c>
+      <c r="E16" s="66">
+        <v>9915.772727272728</v>
+      </c>
+      <c r="F16" s="66">
+        <v>9077.08</v>
+      </c>
+      <c r="G16" s="66">
+        <v>9334.8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="C16" s="66">
-        <v>0.6440457688704533</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.43171165773893433</v>
-      </c>
-      <c r="E16" s="63">
-        <v>0.3538133315885649</v>
-      </c>
-      <c r="F16" s="63">
-        <v>0.31158719566529075</v>
-      </c>
-      <c r="G16" s="63">
-        <v>0.3112549289361249</v>
-      </c>
-      <c r="H16" s="65" t="s">
+      <c r="C17" s="60">
+        <v>0</v>
+      </c>
+      <c r="D17" s="60">
+        <v>0</v>
+      </c>
+      <c r="E17" s="60">
+        <v>0</v>
+      </c>
+      <c r="F17" s="60">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="61" t="s">
+      <c r="C18" s="67">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="67">
+        <v>2058.3333333333335</v>
+      </c>
+      <c r="E18" s="64">
+        <v>1733.215909090909</v>
+      </c>
+      <c r="F18" s="64">
+        <v>1569.72615</v>
+      </c>
+      <c r="G18" s="64">
+        <v>1615.5256657500001</v>
+      </c>
+      <c r="H18" s="65" t="s">
         <v>274</v>
       </c>
-      <c r="C17" s="66">
-        <v>0.19494549648827347</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.10880673808852552</v>
-      </c>
-      <c r="E17" s="63">
-        <v>0.08910177919644068</v>
-      </c>
-      <c r="F17" s="63">
-        <v>0.07840507983728856</v>
-      </c>
-      <c r="G17" s="63">
-        <v>0.07825870088018447</v>
-      </c>
-      <c r="H17" s="65" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="61" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="61" t="s">
-        <v>276</v>
-      </c>
-      <c r="C18" s="63">
-        <v>0.13664054758023902</v>
-      </c>
-      <c r="D18" s="63">
-        <v>0.40710459543276006</v>
-      </c>
-      <c r="E18" s="63">
-        <v>0.5065101671706244</v>
-      </c>
-      <c r="F18" s="63">
-        <v>0.5605212999332692</v>
-      </c>
-      <c r="G18" s="63">
-        <v>0.5612931978259396</v>
-      </c>
-      <c r="H18" s="65" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="61" t="s">
-        <v>278</v>
-      </c>
-      <c r="C19" s="67">
-        <v>3</v>
-      </c>
-      <c r="D19" s="67">
-        <v>3</v>
-      </c>
-      <c r="E19" s="67">
-        <v>3</v>
-      </c>
-      <c r="F19" s="67">
-        <v>3</v>
-      </c>
-      <c r="G19" s="67">
-        <v>3</v>
-      </c>
-      <c r="H19" s="65" t="s">
-        <v>279</v>
+      <c r="C19" s="68">
+        <v>1522.75</v>
+      </c>
+      <c r="D19" s="68">
+        <v>7314.722222222223</v>
+      </c>
+      <c r="E19" s="68">
+        <v>9536.363636363636</v>
+      </c>
+      <c r="F19" s="68">
+        <v>10943.64</v>
+      </c>
+      <c r="G19" s="68">
+        <v>11308.64</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="61" t="s">
-        <v>186</v>
-      </c>
-      <c r="C20" s="68">
-        <v>3.6254310344827587</v>
-      </c>
-      <c r="D20" s="68">
-        <v>19.917241379310344</v>
-      </c>
-      <c r="E20" s="68">
-        <v>31.14353448275862</v>
-      </c>
-      <c r="F20" s="68">
-        <v>40.30905172413793</v>
-      </c>
-      <c r="G20" s="68">
-        <v>41.61997126436781</v>
+        <v>276</v>
+      </c>
+      <c r="C20" s="69">
+        <v>0.6440457688704533</v>
+      </c>
+      <c r="D20" s="63">
+        <v>0.43171165773893433</v>
+      </c>
+      <c r="E20" s="63">
+        <v>0.3538133315885649</v>
+      </c>
+      <c r="F20" s="63">
+        <v>0.31158719566529075</v>
+      </c>
+      <c r="G20" s="63">
+        <v>0.3112549289361249</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="61" t="s">
+        <v>278</v>
+      </c>
+      <c r="C21" s="69">
+        <v>0.19494549648827347</v>
+      </c>
+      <c r="D21" s="63">
+        <v>0.10880673808852552</v>
+      </c>
+      <c r="E21" s="63">
+        <v>0.08910177919644068</v>
+      </c>
+      <c r="F21" s="63">
+        <v>0.07840507983728856</v>
+      </c>
+      <c r="G21" s="63">
+        <v>0.07825870088018447</v>
+      </c>
+      <c r="H21" s="65" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="61" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="63">
+        <v>0.13664054758023902</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.40710459543276006</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0.5065101671706244</v>
+      </c>
+      <c r="F22" s="63">
+        <v>0.5605212999332692</v>
+      </c>
+      <c r="G22" s="63">
+        <v>0.5612931978259396</v>
+      </c>
+      <c r="H22" s="65" t="s">
         <v>281</v>
       </c>
-      <c r="C21" s="30" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" s="70">
+        <v>3</v>
+      </c>
+      <c r="D23" s="70">
+        <v>3</v>
+      </c>
+      <c r="E23" s="70">
+        <v>3</v>
+      </c>
+      <c r="F23" s="70">
+        <v>3</v>
+      </c>
+      <c r="G23" s="70">
+        <v>3</v>
+      </c>
+      <c r="H23" s="65" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="71">
+        <v>3.6254310344827587</v>
+      </c>
+      <c r="D24" s="71">
+        <v>19.917241379310344</v>
+      </c>
+      <c r="E24" s="71">
+        <v>31.14353448275862</v>
+      </c>
+      <c r="F24" s="71">
+        <v>40.30905172413793</v>
+      </c>
+      <c r="G24" s="71">
+        <v>41.61997126436781</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="61" t="s">
+        <v>285</v>
+      </c>
+      <c r="C25" s="30" t="str">
         <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="69" t="str">
+      <c r="D25" s="72" t="str">
         <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="69" t="str">
+      <c r="E25" s="72" t="str">
         <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="69" t="str">
+      <c r="F25" s="72" t="str">
         <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="69" t="str">
+      <c r="G25" s="72" t="str">
         <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H25" s="65" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="61" t="s">
-        <v>282</v>
-      </c>
-      <c r="C22" s="70">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="61" t="s">
+        <v>286</v>
+      </c>
+      <c r="C26" s="73">
         <v>3</v>
       </c>
-      <c r="D22" s="70">
+      <c r="D26" s="73">
         <v>10</v>
       </c>
-      <c r="E22" s="71">
+      <c r="E26" s="74">
         <v>21</v>
       </c>
-      <c r="F22" s="67">
+      <c r="F26" s="70">
         <v>35</v>
       </c>
-      <c r="G22" s="67">
+      <c r="G26" s="70">
         <v>49</v>
       </c>
-      <c r="H22" s="65" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="61" t="s">
+      <c r="H26" s="65" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="C23" s="67">
+      <c r="C27" s="70">
         <v>106</v>
       </c>
-      <c r="D23" s="67">
+      <c r="D27" s="70">
         <v>314</v>
       </c>
-      <c r="E23" s="67">
+      <c r="E27" s="70">
         <v>652</v>
       </c>
-      <c r="F23" s="67">
+      <c r="F27" s="70">
         <v>1067</v>
       </c>
-      <c r="G23" s="67">
+      <c r="G27" s="70">
         <v>1480</v>
       </c>
-      <c r="H23" s="65" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5" t="s">
+      <c r="H27" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="72" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C29" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D26" s="73" t="s">
+      <c r="D29" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74" t="s">
+      <c r="E29" s="5"/>
+      <c r="F29" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="72" t="s">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="75" t="s">
         <v>293</v>
       </c>
-      <c r="C27" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="D27" s="73" t="s">
+      <c r="C30" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74" t="s">
+      <c r="D30" s="76" t="s">
         <v>295</v>
       </c>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="72" t="s">
+      <c r="E30" s="76"/>
+      <c r="F30" s="77" t="s">
         <v>296</v>
       </c>
-      <c r="C28" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="D28" s="73" t="s">
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="75" t="s">
         <v>297</v>
       </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74" t="s">
+      <c r="C31" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D31" s="76" t="s">
         <v>298</v>
       </c>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="72" t="s">
+      <c r="E31" s="76"/>
+      <c r="F31" s="77" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="D29" s="73" t="s">
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="75" t="s">
         <v>300</v>
       </c>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74" t="s">
+      <c r="C32" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D32" s="76" t="s">
         <v>301</v>
       </c>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="72" t="s">
+      <c r="E32" s="76"/>
+      <c r="F32" s="77" t="s">
         <v>302</v>
       </c>
-      <c r="C30" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="D30" s="73" t="s">
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="75" t="s">
         <v>303</v>
       </c>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74" t="s">
+      <c r="C33" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D33" s="76" t="s">
         <v>304</v>
       </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="72" t="s">
+      <c r="E33" s="76"/>
+      <c r="F33" s="77" t="s">
         <v>305</v>
       </c>
-      <c r="C31" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="D31" s="73" t="s">
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="75" t="s">
         <v>306</v>
       </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="74" t="s">
+      <c r="C34" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D34" s="76" t="s">
         <v>307</v>
       </c>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="72" t="s">
+      <c r="E34" s="76"/>
+      <c r="F34" s="77" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="D32" s="73" t="s">
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="E32" s="73"/>
-      <c r="F32" s="74" t="s">
+      <c r="C35" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D35" s="76" t="s">
         <v>310</v>
       </c>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="72" t="s">
-        <v>259</v>
-      </c>
-      <c r="C34" s="61" t="s">
+      <c r="E35" s="76"/>
+      <c r="F35" s="77" t="s">
         <v>311</v>
       </c>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="75" t="s">
         <v>312</v>
       </c>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
+      <c r="C36" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D36" s="76" t="s">
+        <v>313</v>
+      </c>
+      <c r="E36" s="76"/>
+      <c r="F36" s="77" t="s">
+        <v>314</v>
+      </c>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="75" t="s">
+        <v>259</v>
+      </c>
+      <c r="C38" s="61" t="s">
+        <v>315</v>
+      </c>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="78" t="s">
+        <v>316</v>
+      </c>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -4391,8 +4487,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4438,48 +4542,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="312">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -876,18 +876,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -922,9 +910,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1275,7 +1260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1364,15 +1349,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3796,7 +3772,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4045,458 +4021,352 @@
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="61" t="s">
-        <v>110</v>
+        <v>272</v>
       </c>
       <c r="C16" s="66">
-        <v>13866.166666666666</v>
-      </c>
-      <c r="D16" s="66">
-        <v>11602.666666666666</v>
-      </c>
-      <c r="E16" s="66">
-        <v>9915.772727272728</v>
-      </c>
-      <c r="F16" s="66">
-        <v>9077.08</v>
-      </c>
-      <c r="G16" s="66">
-        <v>9334.8</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="C17" s="60">
-        <v>0</v>
-      </c>
-      <c r="D17" s="60">
-        <v>0</v>
-      </c>
-      <c r="E17" s="60">
-        <v>0</v>
-      </c>
-      <c r="F17" s="60">
-        <v>0</v>
-      </c>
-      <c r="G17" s="60">
-        <v>0</v>
+        <v>0.6440457688704533</v>
+      </c>
+      <c r="D16" s="63">
+        <v>0.43171165773893433</v>
+      </c>
+      <c r="E16" s="63">
+        <v>0.3538133315885649</v>
+      </c>
+      <c r="F16" s="63">
+        <v>0.31158719566529075</v>
+      </c>
+      <c r="G16" s="63">
+        <v>0.3112549289361249</v>
+      </c>
+      <c r="H16" s="65" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="66">
+        <v>0.19494549648827347</v>
+      </c>
+      <c r="D17" s="63">
+        <v>0.10880673808852552</v>
+      </c>
+      <c r="E17" s="63">
+        <v>0.08910177919644068</v>
+      </c>
+      <c r="F17" s="63">
+        <v>0.07840507983728856</v>
+      </c>
+      <c r="G17" s="63">
+        <v>0.07825870088018447</v>
+      </c>
+      <c r="H17" s="65" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="C18" s="67">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="67">
-        <v>2058.3333333333335</v>
-      </c>
-      <c r="E18" s="64">
-        <v>1733.215909090909</v>
-      </c>
-      <c r="F18" s="64">
-        <v>1569.72615</v>
-      </c>
-      <c r="G18" s="64">
-        <v>1615.5256657500001</v>
+      <c r="B18" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="63">
+        <v>0.13664054758023902</v>
+      </c>
+      <c r="D18" s="63">
+        <v>0.40710459543276006</v>
+      </c>
+      <c r="E18" s="63">
+        <v>0.5065101671706244</v>
+      </c>
+      <c r="F18" s="63">
+        <v>0.5605212999332692</v>
+      </c>
+      <c r="G18" s="63">
+        <v>0.5612931978259396</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="61" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19" s="68">
-        <v>1522.75</v>
-      </c>
-      <c r="D19" s="68">
-        <v>7314.722222222223</v>
-      </c>
-      <c r="E19" s="68">
-        <v>9536.363636363636</v>
-      </c>
-      <c r="F19" s="68">
-        <v>10943.64</v>
-      </c>
-      <c r="G19" s="68">
-        <v>11308.64</v>
+        <v>278</v>
+      </c>
+      <c r="C19" s="67">
+        <v>3</v>
+      </c>
+      <c r="D19" s="67">
+        <v>3</v>
+      </c>
+      <c r="E19" s="67">
+        <v>3</v>
+      </c>
+      <c r="F19" s="67">
+        <v>3</v>
+      </c>
+      <c r="G19" s="67">
+        <v>3</v>
+      </c>
+      <c r="H19" s="65" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="61" t="s">
-        <v>276</v>
-      </c>
-      <c r="C20" s="69">
-        <v>0.6440457688704533</v>
-      </c>
-      <c r="D20" s="63">
-        <v>0.43171165773893433</v>
-      </c>
-      <c r="E20" s="63">
-        <v>0.3538133315885649</v>
-      </c>
-      <c r="F20" s="63">
-        <v>0.31158719566529075</v>
-      </c>
-      <c r="G20" s="63">
-        <v>0.3112549289361249</v>
+        <v>186</v>
+      </c>
+      <c r="C20" s="68">
+        <v>3.6254310344827587</v>
+      </c>
+      <c r="D20" s="68">
+        <v>19.917241379310344</v>
+      </c>
+      <c r="E20" s="68">
+        <v>31.14353448275862</v>
+      </c>
+      <c r="F20" s="68">
+        <v>40.30905172413793</v>
+      </c>
+      <c r="G20" s="68">
+        <v>41.61997126436781</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="61" t="s">
-        <v>278</v>
-      </c>
-      <c r="C21" s="69">
-        <v>0.19494549648827347</v>
-      </c>
-      <c r="D21" s="63">
-        <v>0.10880673808852552</v>
-      </c>
-      <c r="E21" s="63">
-        <v>0.08910177919644068</v>
-      </c>
-      <c r="F21" s="63">
-        <v>0.07840507983728856</v>
-      </c>
-      <c r="G21" s="63">
-        <v>0.07825870088018447</v>
+        <v>281</v>
+      </c>
+      <c r="C21" s="30" t="str">
+        <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="69" t="str">
+        <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="69" t="str">
+        <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="69" t="str">
+        <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="69" t="str">
+        <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>279</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="61" t="s">
-        <v>280</v>
-      </c>
-      <c r="C22" s="63">
-        <v>0.13664054758023902</v>
-      </c>
-      <c r="D22" s="63">
-        <v>0.40710459543276006</v>
-      </c>
-      <c r="E22" s="63">
-        <v>0.5065101671706244</v>
-      </c>
-      <c r="F22" s="63">
-        <v>0.5605212999332692</v>
-      </c>
-      <c r="G22" s="63">
-        <v>0.5612931978259396</v>
+        <v>282</v>
+      </c>
+      <c r="C22" s="70">
+        <v>3</v>
+      </c>
+      <c r="D22" s="70">
+        <v>10</v>
+      </c>
+      <c r="E22" s="71">
+        <v>21</v>
+      </c>
+      <c r="F22" s="67">
+        <v>35</v>
+      </c>
+      <c r="G22" s="67">
+        <v>49</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="61" t="s">
-        <v>282</v>
-      </c>
-      <c r="C23" s="70">
-        <v>3</v>
-      </c>
-      <c r="D23" s="70">
-        <v>3</v>
-      </c>
-      <c r="E23" s="70">
-        <v>3</v>
-      </c>
-      <c r="F23" s="70">
-        <v>3</v>
-      </c>
-      <c r="G23" s="70">
-        <v>3</v>
-      </c>
-      <c r="H23" s="65" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="61" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="71">
-        <v>3.6254310344827587</v>
-      </c>
-      <c r="D24" s="71">
-        <v>19.917241379310344</v>
-      </c>
-      <c r="E24" s="71">
-        <v>31.14353448275862</v>
-      </c>
-      <c r="F24" s="71">
-        <v>40.30905172413793</v>
-      </c>
-      <c r="G24" s="71">
-        <v>41.61997126436781</v>
-      </c>
-      <c r="H24" s="65" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="61" t="s">
+      <c r="C24" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C25" s="30" t="str">
-        <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="72" t="str">
-        <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="72" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="72" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="72" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="61" t="s">
+      <c r="D24" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C26" s="73">
-        <v>3</v>
-      </c>
-      <c r="D26" s="73">
-        <v>10</v>
-      </c>
-      <c r="E26" s="74">
-        <v>21</v>
-      </c>
-      <c r="F26" s="70">
-        <v>35</v>
-      </c>
-      <c r="G26" s="70">
-        <v>49</v>
-      </c>
-      <c r="H26" s="65" t="s">
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="C27" s="70">
-        <v>106</v>
-      </c>
-      <c r="D27" s="70">
-        <v>314</v>
-      </c>
-      <c r="E27" s="70">
-        <v>652</v>
-      </c>
-      <c r="F27" s="70">
-        <v>1067</v>
-      </c>
-      <c r="G27" s="70">
-        <v>1480</v>
-      </c>
-      <c r="H27" s="65" t="s">
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="72" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
+      <c r="C25" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D25" s="73" t="s">
         <v>290</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E25" s="73"/>
+      <c r="F25" s="74" t="s">
         <v>291</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5" t="s">
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="72" t="s">
         <v>292</v>
       </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="C26" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D26" s="73" t="s">
+        <v>293</v>
+      </c>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74" t="s">
+        <v>294</v>
+      </c>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="72" t="s">
+        <v>295</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D27" s="73" t="s">
+        <v>296</v>
+      </c>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74" t="s">
+        <v>297</v>
+      </c>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="72" t="s">
+        <v>298</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D28" s="73" t="s">
+        <v>299</v>
+      </c>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74" t="s">
+        <v>300</v>
+      </c>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="72" t="s">
+        <v>301</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D29" s="73" t="s">
+        <v>302</v>
+      </c>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74" t="s">
+        <v>303</v>
+      </c>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="75" t="s">
-        <v>293</v>
+      <c r="B30" s="72" t="s">
+        <v>304</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="D30" s="76" t="s">
-        <v>295</v>
-      </c>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77" t="s">
-        <v>296</v>
-      </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
+        <v>289</v>
+      </c>
+      <c r="D30" s="73" t="s">
+        <v>305</v>
+      </c>
+      <c r="E30" s="73"/>
+      <c r="F30" s="74" t="s">
+        <v>306</v>
+      </c>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="75" t="s">
-        <v>297</v>
+      <c r="B31" s="72" t="s">
+        <v>307</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="D31" s="76" t="s">
-        <v>298</v>
-      </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77" t="s">
-        <v>299</v>
-      </c>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="75" t="s">
-        <v>300</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="D32" s="76" t="s">
-        <v>301</v>
-      </c>
-      <c r="E32" s="76"/>
-      <c r="F32" s="77" t="s">
-        <v>302</v>
-      </c>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="75" t="s">
-        <v>303</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="D33" s="76" t="s">
-        <v>304</v>
-      </c>
-      <c r="E33" s="76"/>
-      <c r="F33" s="77" t="s">
-        <v>305</v>
-      </c>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="75" t="s">
-        <v>306</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="D34" s="76" t="s">
-        <v>307</v>
-      </c>
-      <c r="E34" s="76"/>
-      <c r="F34" s="77" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" s="73" t="s">
         <v>308</v>
       </c>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E31" s="73"/>
+      <c r="F31" s="74" t="s">
+        <v>309</v>
+      </c>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="C33" s="61" t="s">
+        <v>310</v>
+      </c>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="75" t="s">
-        <v>309</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="D35" s="76" t="s">
-        <v>310</v>
-      </c>
-      <c r="E35" s="76"/>
-      <c r="F35" s="77" t="s">
         <v>311</v>
       </c>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="75" t="s">
-        <v>312</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="D36" s="76" t="s">
-        <v>313</v>
-      </c>
-      <c r="E36" s="76"/>
-      <c r="F36" s="77" t="s">
-        <v>314</v>
-      </c>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="C38" s="61" t="s">
-        <v>315</v>
-      </c>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="78" t="s">
-        <v>316</v>
-      </c>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4542,48 +4412,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="317">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -876,6 +876,18 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -910,6 +922,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1260,7 +1275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1349,6 +1364,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3772,7 +3796,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4021,352 +4045,458 @@
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="66">
+        <v>13866.166666666666</v>
+      </c>
+      <c r="D16" s="66">
+        <v>11602.666666666666</v>
+      </c>
+      <c r="E16" s="66">
+        <v>9915.772727272728</v>
+      </c>
+      <c r="F16" s="66">
+        <v>9077.08</v>
+      </c>
+      <c r="G16" s="66">
+        <v>9334.8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="C16" s="66">
-        <v>0.6440457688704533</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.43171165773893433</v>
-      </c>
-      <c r="E16" s="63">
-        <v>0.3538133315885649</v>
-      </c>
-      <c r="F16" s="63">
-        <v>0.31158719566529075</v>
-      </c>
-      <c r="G16" s="63">
-        <v>0.3112549289361249</v>
-      </c>
-      <c r="H16" s="65" t="s">
+      <c r="C17" s="60">
+        <v>0</v>
+      </c>
+      <c r="D17" s="60">
+        <v>0</v>
+      </c>
+      <c r="E17" s="60">
+        <v>0</v>
+      </c>
+      <c r="F17" s="60">
+        <v>0</v>
+      </c>
+      <c r="G17" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="61" t="s">
+      <c r="C18" s="67">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="67">
+        <v>2058.3333333333335</v>
+      </c>
+      <c r="E18" s="64">
+        <v>1733.215909090909</v>
+      </c>
+      <c r="F18" s="64">
+        <v>1569.72615</v>
+      </c>
+      <c r="G18" s="64">
+        <v>1615.5256657500001</v>
+      </c>
+      <c r="H18" s="65" t="s">
         <v>274</v>
       </c>
-      <c r="C17" s="66">
-        <v>0.19494549648827347</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.10880673808852552</v>
-      </c>
-      <c r="E17" s="63">
-        <v>0.08910177919644068</v>
-      </c>
-      <c r="F17" s="63">
-        <v>0.07840507983728856</v>
-      </c>
-      <c r="G17" s="63">
-        <v>0.07825870088018447</v>
-      </c>
-      <c r="H17" s="65" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="61" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="61" t="s">
-        <v>276</v>
-      </c>
-      <c r="C18" s="63">
-        <v>0.13664054758023902</v>
-      </c>
-      <c r="D18" s="63">
-        <v>0.40710459543276006</v>
-      </c>
-      <c r="E18" s="63">
-        <v>0.5065101671706244</v>
-      </c>
-      <c r="F18" s="63">
-        <v>0.5605212999332692</v>
-      </c>
-      <c r="G18" s="63">
-        <v>0.5612931978259396</v>
-      </c>
-      <c r="H18" s="65" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="61" t="s">
-        <v>278</v>
-      </c>
-      <c r="C19" s="67">
-        <v>3</v>
-      </c>
-      <c r="D19" s="67">
-        <v>3</v>
-      </c>
-      <c r="E19" s="67">
-        <v>3</v>
-      </c>
-      <c r="F19" s="67">
-        <v>3</v>
-      </c>
-      <c r="G19" s="67">
-        <v>3</v>
-      </c>
-      <c r="H19" s="65" t="s">
-        <v>279</v>
+      <c r="C19" s="68">
+        <v>1522.75</v>
+      </c>
+      <c r="D19" s="68">
+        <v>7314.722222222223</v>
+      </c>
+      <c r="E19" s="68">
+        <v>9536.363636363636</v>
+      </c>
+      <c r="F19" s="68">
+        <v>10943.64</v>
+      </c>
+      <c r="G19" s="68">
+        <v>11308.64</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="61" t="s">
-        <v>186</v>
-      </c>
-      <c r="C20" s="68">
-        <v>3.6254310344827587</v>
-      </c>
-      <c r="D20" s="68">
-        <v>19.917241379310344</v>
-      </c>
-      <c r="E20" s="68">
-        <v>31.14353448275862</v>
-      </c>
-      <c r="F20" s="68">
-        <v>40.30905172413793</v>
-      </c>
-      <c r="G20" s="68">
-        <v>41.61997126436781</v>
+        <v>276</v>
+      </c>
+      <c r="C20" s="69">
+        <v>0.6440457688704533</v>
+      </c>
+      <c r="D20" s="63">
+        <v>0.43171165773893433</v>
+      </c>
+      <c r="E20" s="63">
+        <v>0.3538133315885649</v>
+      </c>
+      <c r="F20" s="63">
+        <v>0.31158719566529075</v>
+      </c>
+      <c r="G20" s="63">
+        <v>0.3112549289361249</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="61" t="s">
+        <v>278</v>
+      </c>
+      <c r="C21" s="69">
+        <v>0.19494549648827347</v>
+      </c>
+      <c r="D21" s="63">
+        <v>0.10880673808852552</v>
+      </c>
+      <c r="E21" s="63">
+        <v>0.08910177919644068</v>
+      </c>
+      <c r="F21" s="63">
+        <v>0.07840507983728856</v>
+      </c>
+      <c r="G21" s="63">
+        <v>0.07825870088018447</v>
+      </c>
+      <c r="H21" s="65" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="61" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="63">
+        <v>0.13664054758023902</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.40710459543276006</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0.5065101671706244</v>
+      </c>
+      <c r="F22" s="63">
+        <v>0.5605212999332692</v>
+      </c>
+      <c r="G22" s="63">
+        <v>0.5612931978259396</v>
+      </c>
+      <c r="H22" s="65" t="s">
         <v>281</v>
       </c>
-      <c r="C21" s="30" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" s="70">
+        <v>3</v>
+      </c>
+      <c r="D23" s="70">
+        <v>3</v>
+      </c>
+      <c r="E23" s="70">
+        <v>3</v>
+      </c>
+      <c r="F23" s="70">
+        <v>3</v>
+      </c>
+      <c r="G23" s="70">
+        <v>3</v>
+      </c>
+      <c r="H23" s="65" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="71">
+        <v>3.6254310344827587</v>
+      </c>
+      <c r="D24" s="71">
+        <v>19.917241379310344</v>
+      </c>
+      <c r="E24" s="71">
+        <v>31.14353448275862</v>
+      </c>
+      <c r="F24" s="71">
+        <v>40.30905172413793</v>
+      </c>
+      <c r="G24" s="71">
+        <v>41.61997126436781</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="61" t="s">
+        <v>285</v>
+      </c>
+      <c r="C25" s="30" t="str">
         <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="69" t="str">
+      <c r="D25" s="72" t="str">
         <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="69" t="str">
+      <c r="E25" s="72" t="str">
         <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="69" t="str">
+      <c r="F25" s="72" t="str">
         <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="69" t="str">
+      <c r="G25" s="72" t="str">
         <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H25" s="65" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="61" t="s">
-        <v>282</v>
-      </c>
-      <c r="C22" s="70">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="61" t="s">
+        <v>286</v>
+      </c>
+      <c r="C26" s="73">
         <v>3</v>
       </c>
-      <c r="D22" s="70">
+      <c r="D26" s="73">
         <v>10</v>
       </c>
-      <c r="E22" s="71">
+      <c r="E26" s="74">
         <v>21</v>
       </c>
-      <c r="F22" s="67">
+      <c r="F26" s="70">
         <v>35</v>
       </c>
-      <c r="G22" s="67">
+      <c r="G26" s="70">
         <v>49</v>
       </c>
-      <c r="H22" s="65" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
+      <c r="H26" s="65" t="s">
         <v>287</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="72" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="70">
+        <v>106</v>
+      </c>
+      <c r="D27" s="70">
+        <v>314</v>
+      </c>
+      <c r="E27" s="70">
+        <v>652</v>
+      </c>
+      <c r="F27" s="70">
+        <v>1067</v>
+      </c>
+      <c r="G27" s="70">
+        <v>1480</v>
+      </c>
+      <c r="H27" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="C25" s="30" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="C29" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74" t="s">
+      <c r="D29" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="72" t="s">
+      <c r="E29" s="5"/>
+      <c r="F29" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="C26" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D26" s="73" t="s">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="75" t="s">
         <v>293</v>
       </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74" t="s">
+      <c r="C30" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="72" t="s">
+      <c r="D30" s="76" t="s">
         <v>295</v>
       </c>
-      <c r="C27" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D27" s="73" t="s">
+      <c r="E30" s="76"/>
+      <c r="F30" s="77" t="s">
         <v>296</v>
       </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74" t="s">
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="75" t="s">
         <v>297</v>
       </c>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="72" t="s">
+      <c r="C31" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D31" s="76" t="s">
         <v>298</v>
       </c>
-      <c r="C28" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D28" s="73" t="s">
+      <c r="E31" s="76"/>
+      <c r="F31" s="77" t="s">
         <v>299</v>
       </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74" t="s">
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="75" t="s">
         <v>300</v>
       </c>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="72" t="s">
+      <c r="C32" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D32" s="76" t="s">
         <v>301</v>
       </c>
-      <c r="C29" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D29" s="73" t="s">
+      <c r="E32" s="76"/>
+      <c r="F32" s="77" t="s">
         <v>302</v>
       </c>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74" t="s">
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="75" t="s">
         <v>303</v>
       </c>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="72" t="s">
+      <c r="C33" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D33" s="76" t="s">
         <v>304</v>
       </c>
-      <c r="C30" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D30" s="73" t="s">
+      <c r="E33" s="76"/>
+      <c r="F33" s="77" t="s">
         <v>305</v>
       </c>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74" t="s">
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="75" t="s">
         <v>306</v>
       </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="72" t="s">
+      <c r="C34" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D34" s="76" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D31" s="73" t="s">
+      <c r="E34" s="76"/>
+      <c r="F34" s="77" t="s">
         <v>308</v>
       </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="74" t="s">
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="72" t="s">
+      <c r="C35" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D35" s="76" t="s">
+        <v>310</v>
+      </c>
+      <c r="E35" s="76"/>
+      <c r="F35" s="77" t="s">
+        <v>311</v>
+      </c>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="75" t="s">
+        <v>312</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="D36" s="76" t="s">
+        <v>313</v>
+      </c>
+      <c r="E36" s="76"/>
+      <c r="F36" s="77" t="s">
+        <v>314</v>
+      </c>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="75" t="s">
         <v>259</v>
       </c>
-      <c r="C33" s="61" t="s">
-        <v>310</v>
-      </c>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="75" t="s">
-        <v>311</v>
-      </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
+      <c r="C38" s="61" t="s">
+        <v>315</v>
+      </c>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="78" t="s">
+        <v>316</v>
+      </c>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4412,48 +4542,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Microschool_Startup.xlsx
@@ -639,7 +639,7 @@
     <t>COVENANT CHECKS</t>
   </si>
   <si>
-    <t>DSCR ≥ 1.20x</t>
+    <t>DSCR ≥ 1.25x</t>
   </si>
   <si>
     <t>Cash Reserve ≥ 2.0 Months</t>
@@ -666,7 +666,7 @@
     <t>POLICY FLAGS</t>
   </si>
   <si>
-    <t>DSCR ≥ 1.20x (2026-27)</t>
+    <t>DSCR ≥ 1.25x (2026-27)</t>
   </si>
   <si>
     <t>3.63x</t>
@@ -756,7 +756,7 @@
     <t>Microschool  |  AZ  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 27, 2026</t>
+    <t>Prepared April 29, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -783,7 +783,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>
@@ -843,7 +843,7 @@
     <t>Bright Horizons Microschool — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -2904,23 +2904,23 @@
         <v>193</v>
       </c>
       <c r="B14" s="35" t="str">
-        <f>IF(B5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(B5&gt;=1.25,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="C14" s="35" t="str">
-        <f>IF(C5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(C5&gt;=1.25,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="D14" s="35" t="str">
-        <f>IF(D5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(D5&gt;=1.25,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="E14" s="35" t="str">
-        <f>IF(E5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(E5&gt;=1.25,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="F14" s="35" t="str">
-        <f>IF(F5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(F5&gt;=1.25,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -4580,10 +4580,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
